--- a/research/traditional_assets/database/data/netherlands/netherlands_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_oil_gas_distribution.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07031265058164096</v>
+        <v>0.07016463394314032</v>
       </c>
       <c r="C2">
-        <v>7741.705130136082</v>
+        <v>7673.598295863905</v>
       </c>
       <c r="D2">
-        <v>7741.705130136082</v>
+        <v>7756.135295863905</v>
       </c>
       <c r="E2">
-        <v>-2975.7</v>
+        <v>-2893.163</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>82.53700000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.1516111</v>
       </c>
       <c r="N2">
-        <v>394.2857142857143</v>
+        <v>390.1341031857143</v>
       </c>
       <c r="O2">
-        <v>101.7257142857143</v>
+        <v>100.6545986219143</v>
       </c>
       <c r="P2">
-        <v>292.5600000000001</v>
+        <v>289.4795045638</v>
       </c>
       <c r="Q2">
-        <v>632.5600000000001</v>
+        <v>629.4795045638</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07031265058164096</v>
+        <v>0.0704963716597377</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5703550036890923</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>94.97173622204505</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07016463394314032</v>
+        <v>0.07001661730463968</v>
       </c>
       <c r="C3">
-        <v>7673.598295863905</v>
+        <v>7605.545356317593</v>
       </c>
       <c r="D3">
-        <v>7756.135295863905</v>
+        <v>7770.619356317593</v>
       </c>
       <c r="E3">
-        <v>-2893.163</v>
+        <v>-2810.626</v>
       </c>
       <c r="F3">
-        <v>82.53700000000001</v>
+        <v>165.074</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1527,28 +1527,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M3">
-        <v>4.1516111</v>
+        <v>8.3032222</v>
       </c>
       <c r="N3">
-        <v>390.1341031857143</v>
+        <v>385.9824920857143</v>
       </c>
       <c r="O3">
-        <v>100.6545986219143</v>
+        <v>99.5834829581143</v>
       </c>
       <c r="P3">
-        <v>289.4795045638</v>
+        <v>286.3990091276</v>
       </c>
       <c r="Q3">
-        <v>629.4795045638</v>
+        <v>626.3990091276</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0704963716597377</v>
+        <v>0.07068384214759152</v>
       </c>
       <c r="T3">
-        <v>0.5703550036890923</v>
+        <v>0.574684576156848</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>94.97173622204505</v>
+        <v>47.48586811102253</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07001661730463968</v>
+        <v>0.06986860066613905</v>
       </c>
       <c r="C4">
-        <v>7605.545356317593</v>
+        <v>7537.546613996354</v>
       </c>
       <c r="D4">
-        <v>7770.619356317593</v>
+        <v>7785.157613996354</v>
       </c>
       <c r="E4">
-        <v>-2810.626</v>
+        <v>-2728.089</v>
       </c>
       <c r="F4">
-        <v>165.074</v>
+        <v>247.611</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M4">
-        <v>8.3032222</v>
+        <v>12.4548333</v>
       </c>
       <c r="N4">
-        <v>385.9824920857143</v>
+        <v>381.8308809857143</v>
       </c>
       <c r="O4">
-        <v>99.5834829581143</v>
+        <v>98.5123672943143</v>
       </c>
       <c r="P4">
-        <v>286.3990091276</v>
+        <v>283.3185136914</v>
       </c>
       <c r="Q4">
-        <v>626.3990091276</v>
+        <v>623.3185136914001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07068384214759152</v>
+        <v>0.07087517800632892</v>
       </c>
       <c r="T4">
-        <v>0.574684576156848</v>
+        <v>0.5791034181600213</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>47.48586811102253</v>
+        <v>31.65724540734835</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06986860066613905</v>
+        <v>0.06972058402763842</v>
       </c>
       <c r="C5">
-        <v>7537.546613996354</v>
+        <v>7469.602373667458</v>
       </c>
       <c r="D5">
-        <v>7785.157613996354</v>
+        <v>7799.750373667458</v>
       </c>
       <c r="E5">
-        <v>-2728.089</v>
+        <v>-2645.552</v>
       </c>
       <c r="F5">
-        <v>247.611</v>
+        <v>330.148</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1691,28 +1691,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M5">
-        <v>12.4548333</v>
+        <v>16.6064444</v>
       </c>
       <c r="N5">
-        <v>381.8308809857143</v>
+        <v>377.6792698857143</v>
       </c>
       <c r="O5">
-        <v>98.5123672943143</v>
+        <v>97.4412516305143</v>
       </c>
       <c r="P5">
-        <v>283.3185136914</v>
+        <v>280.2380182552</v>
       </c>
       <c r="Q5">
-        <v>623.3185136914001</v>
+        <v>620.2380182552</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07087517800632892</v>
+        <v>0.07107050002879002</v>
       </c>
       <c r="T5">
-        <v>0.5791034181600213</v>
+        <v>0.583614319371594</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.65724540734835</v>
+        <v>23.74293405551126</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06972058402763842</v>
+        <v>0.06957256738913778</v>
       </c>
       <c r="C6">
-        <v>7469.602373667458</v>
+        <v>7401.712942387537</v>
       </c>
       <c r="D6">
-        <v>7799.750373667458</v>
+        <v>7814.397942387537</v>
       </c>
       <c r="E6">
-        <v>-2645.552</v>
+        <v>-2563.015</v>
       </c>
       <c r="F6">
-        <v>330.148</v>
+        <v>412.6850000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1773,28 +1773,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M6">
-        <v>16.6064444</v>
+        <v>20.7580555</v>
       </c>
       <c r="N6">
-        <v>377.6792698857143</v>
+        <v>373.5276587857143</v>
       </c>
       <c r="O6">
-        <v>97.4412516305143</v>
+        <v>96.3701359667143</v>
       </c>
       <c r="P6">
-        <v>280.2380182552</v>
+        <v>277.157522819</v>
       </c>
       <c r="Q6">
-        <v>620.2380182552</v>
+        <v>617.157522819</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07107050002879002</v>
+        <v>0.07126993409382926</v>
       </c>
       <c r="T6">
-        <v>0.583614319371594</v>
+        <v>0.5882201869244631</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.74293405551126</v>
+        <v>18.99434724440901</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06957256738913778</v>
+        <v>0.06942455075063715</v>
       </c>
       <c r="C7">
-        <v>7401.712942387537</v>
+        <v>7333.878629524104</v>
       </c>
       <c r="D7">
-        <v>7814.397942387537</v>
+        <v>7829.100629524104</v>
       </c>
       <c r="E7">
-        <v>-2563.015</v>
+        <v>-2480.478</v>
       </c>
       <c r="F7">
-        <v>412.6850000000001</v>
+        <v>495.2220000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1855,28 +1855,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M7">
-        <v>20.7580555</v>
+        <v>24.9096666</v>
       </c>
       <c r="N7">
-        <v>373.5276587857143</v>
+        <v>369.3760476857144</v>
       </c>
       <c r="O7">
-        <v>96.3701359667143</v>
+        <v>95.2990203029143</v>
       </c>
       <c r="P7">
-        <v>277.157522819</v>
+        <v>274.0770273828001</v>
       </c>
       <c r="Q7">
-        <v>617.157522819</v>
+        <v>614.0770273828</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07126993409382926</v>
+        <v>0.07147361143684804</v>
       </c>
       <c r="T7">
-        <v>0.5882201869244631</v>
+        <v>0.5929240516593079</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.99434724440901</v>
+        <v>15.82862270367417</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06942455075063715</v>
+        <v>0.06927653411213652</v>
       </c>
       <c r="C8">
-        <v>7333.878629524104</v>
+        <v>7266.099746777351</v>
       </c>
       <c r="D8">
-        <v>7829.100629524104</v>
+        <v>7843.858746777351</v>
       </c>
       <c r="E8">
-        <v>-2480.478</v>
+        <v>-2397.941</v>
       </c>
       <c r="F8">
-        <v>495.222</v>
+        <v>577.759</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1937,28 +1937,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M8">
-        <v>24.9096666</v>
+        <v>29.0612777</v>
       </c>
       <c r="N8">
-        <v>369.3760476857144</v>
+        <v>365.2244365857143</v>
       </c>
       <c r="O8">
-        <v>95.2990203029143</v>
+        <v>94.2279046391143</v>
       </c>
       <c r="P8">
-        <v>274.0770273828001</v>
+        <v>270.9965319466</v>
       </c>
       <c r="Q8">
-        <v>614.0770273828</v>
+        <v>610.9965319466</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07147361143684804</v>
+        <v>0.0716816689377812</v>
       </c>
       <c r="T8">
-        <v>0.5929240516593079</v>
+        <v>0.5977290747755475</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.82862270367418</v>
+        <v>13.56739088886358</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06927653411213652</v>
+        <v>0.06912851747363589</v>
       </c>
       <c r="C9">
-        <v>7266.099746777351</v>
+        <v>7198.376608202169</v>
       </c>
       <c r="D9">
-        <v>7843.858746777351</v>
+        <v>7858.67260820217</v>
       </c>
       <c r="E9">
-        <v>-2397.941</v>
+        <v>-2315.404</v>
       </c>
       <c r="F9">
-        <v>577.7590000000001</v>
+        <v>660.296</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2019,28 +2019,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M9">
-        <v>29.06127770000001</v>
+        <v>33.2128888</v>
       </c>
       <c r="N9">
-        <v>365.2244365857143</v>
+        <v>361.0728254857144</v>
       </c>
       <c r="O9">
-        <v>94.2279046391143</v>
+        <v>93.15678897531431</v>
       </c>
       <c r="P9">
-        <v>270.9965319466</v>
+        <v>267.9160365104</v>
       </c>
       <c r="Q9">
-        <v>610.9965319466</v>
+        <v>607.9160365104001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0716816689377812</v>
+        <v>0.0718942494278651</v>
       </c>
       <c r="T9">
-        <v>0.5977290747755475</v>
+        <v>0.6026385549160529</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>13.56739088886358</v>
+        <v>11.87146702775563</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06912851747363589</v>
+        <v>0.06898050083513525</v>
       </c>
       <c r="C10">
-        <v>7198.376608202169</v>
+        <v>7130.70953023043</v>
       </c>
       <c r="D10">
-        <v>7858.67260820217</v>
+        <v>7873.542530230429</v>
       </c>
       <c r="E10">
-        <v>-2315.404</v>
+        <v>-2232.867</v>
       </c>
       <c r="F10">
-        <v>660.296</v>
+        <v>742.8330000000001</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2101,28 +2101,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M10">
-        <v>33.2128888</v>
+        <v>37.36449990000001</v>
       </c>
       <c r="N10">
-        <v>361.0728254857144</v>
+        <v>356.9212143857143</v>
       </c>
       <c r="O10">
-        <v>93.15678897531431</v>
+        <v>92.0856733115143</v>
       </c>
       <c r="P10">
-        <v>267.9160365104</v>
+        <v>264.8355410742</v>
       </c>
       <c r="Q10">
-        <v>607.9160365104001</v>
+        <v>604.8355410742</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0718942494278651</v>
+        <v>0.07211150201663215</v>
       </c>
       <c r="T10">
-        <v>0.6026385549160529</v>
+        <v>0.6076559357189872</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.87146702775563</v>
+        <v>10.55241513578278</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06898050083513525</v>
+        <v>0.06883248419663462</v>
       </c>
       <c r="C11">
-        <v>7130.70953023043</v>
+        <v>7063.098831693504</v>
       </c>
       <c r="D11">
-        <v>7873.542530230429</v>
+        <v>7888.468831693503</v>
       </c>
       <c r="E11">
-        <v>-2232.867</v>
+        <v>-2150.33</v>
       </c>
       <c r="F11">
-        <v>742.8330000000001</v>
+        <v>825.37</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2183,28 +2183,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M11">
-        <v>37.36449990000001</v>
+        <v>41.516111</v>
       </c>
       <c r="N11">
-        <v>356.9212143857143</v>
+        <v>352.7696032857143</v>
       </c>
       <c r="O11">
-        <v>92.0856733115143</v>
+        <v>91.0145576477143</v>
       </c>
       <c r="P11">
-        <v>264.8355410742</v>
+        <v>261.755045638</v>
       </c>
       <c r="Q11">
-        <v>604.8355410742</v>
+        <v>601.755045638</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07211150201663215</v>
+        <v>0.07233358244070513</v>
       </c>
       <c r="T11">
-        <v>0.6076559357189872</v>
+        <v>0.6127848138730978</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>10.55241513578278</v>
+        <v>9.497173622204507</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06883248419663462</v>
+        <v>0.06880689755813398</v>
       </c>
       <c r="C12">
-        <v>7063.098831693504</v>
+        <v>6983.147779681168</v>
       </c>
       <c r="D12">
-        <v>7888.468831693503</v>
+        <v>7891.054779681168</v>
       </c>
       <c r="E12">
-        <v>-2150.33</v>
+        <v>-2067.793</v>
       </c>
       <c r="F12">
-        <v>825.3700000000001</v>
+        <v>907.907</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2265,45 +2265,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M12">
-        <v>41.516111</v>
+        <v>47.0295826</v>
       </c>
       <c r="N12">
-        <v>352.7696032857143</v>
+        <v>347.2561316857143</v>
       </c>
       <c r="O12">
-        <v>91.0145576477143</v>
+        <v>89.59208197491429</v>
       </c>
       <c r="P12">
-        <v>261.755045638</v>
+        <v>257.6640497108</v>
       </c>
       <c r="Q12">
-        <v>601.755045638</v>
+        <v>597.6640497108</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07233358244070513</v>
+        <v>0.0725606534361056</v>
       </c>
       <c r="T12">
-        <v>0.6127848138730978</v>
+        <v>0.6180289477160646</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>9.497173622204505</v>
+        <v>8.383780856386217</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06880689755813398</v>
+        <v>0.06867001091963336</v>
       </c>
       <c r="C13">
-        <v>6983.147779681168</v>
+        <v>6914.474260329953</v>
       </c>
       <c r="D13">
-        <v>7891.054779681168</v>
+        <v>7904.918260329953</v>
       </c>
       <c r="E13">
-        <v>-2067.793</v>
+        <v>-1985.256</v>
       </c>
       <c r="F13">
-        <v>907.907</v>
+        <v>990.4440000000001</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2347,28 +2347,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M13">
-        <v>47.0295826</v>
+        <v>51.3049992</v>
       </c>
       <c r="N13">
-        <v>347.2561316857143</v>
+        <v>342.9807150857143</v>
       </c>
       <c r="O13">
-        <v>89.59208197491429</v>
+        <v>88.4890244921143</v>
       </c>
       <c r="P13">
-        <v>257.6640497108</v>
+        <v>254.4916905936</v>
       </c>
       <c r="Q13">
-        <v>597.6640497108</v>
+        <v>594.4916905936</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0725606534361056</v>
+        <v>0.07279288513594699</v>
       </c>
       <c r="T13">
-        <v>0.6180289477160646</v>
+        <v>0.6233922664190992</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.383780856386217</v>
+        <v>7.685132451687365</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06867001091963336</v>
+        <v>0.06853312428113272</v>
       </c>
       <c r="C14">
-        <v>6914.474260329953</v>
+        <v>6845.84953910701</v>
       </c>
       <c r="D14">
-        <v>7904.918260329953</v>
+        <v>7918.83053910701</v>
       </c>
       <c r="E14">
-        <v>-1985.256</v>
+        <v>-1902.719</v>
       </c>
       <c r="F14">
-        <v>990.4440000000001</v>
+        <v>1072.981</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2429,28 +2429,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M14">
-        <v>51.3049992</v>
+        <v>55.58041580000001</v>
       </c>
       <c r="N14">
-        <v>342.9807150857143</v>
+        <v>338.7052984857143</v>
       </c>
       <c r="O14">
-        <v>88.4890244921143</v>
+        <v>87.3859670093143</v>
       </c>
       <c r="P14">
-        <v>254.4916905936</v>
+        <v>251.3193314764</v>
       </c>
       <c r="Q14">
-        <v>594.4916905936</v>
+        <v>591.3193314764001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07279288513594699</v>
+        <v>0.07303045549555484</v>
       </c>
       <c r="T14">
-        <v>0.6233922664190992</v>
+        <v>0.6288788798049618</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.685132451687365</v>
+        <v>7.093968416942182</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06853312428113272</v>
+        <v>0.0685728336426321</v>
       </c>
       <c r="C15">
-        <v>6845.84953910701</v>
+        <v>6759.271694842728</v>
       </c>
       <c r="D15">
-        <v>7918.83053910701</v>
+        <v>7914.789694842728</v>
       </c>
       <c r="E15">
-        <v>-1902.719</v>
+        <v>-1820.182</v>
       </c>
       <c r="F15">
-        <v>1072.981</v>
+        <v>1155.518</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2511,45 +2511,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M15">
-        <v>55.58041580000001</v>
+        <v>61.82021300000001</v>
       </c>
       <c r="N15">
-        <v>338.7052984857143</v>
+        <v>332.4655012857143</v>
       </c>
       <c r="O15">
-        <v>87.3859670093143</v>
+        <v>85.77609933171429</v>
       </c>
       <c r="P15">
-        <v>251.3193314764</v>
+        <v>246.689401954</v>
       </c>
       <c r="Q15">
-        <v>591.3193314764001</v>
+        <v>586.689401954</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07303045549555484</v>
+        <v>0.07327355074724662</v>
       </c>
       <c r="T15">
-        <v>0.6288788798049618</v>
+        <v>0.634493088850961</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.093968416942182</v>
+        <v>6.377941698222784</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0685728336426321</v>
+        <v>0.06844856100413145</v>
       </c>
       <c r="C16">
-        <v>6759.271694842728</v>
+        <v>6689.394504126071</v>
       </c>
       <c r="D16">
-        <v>7914.789694842728</v>
+        <v>7927.449504126072</v>
       </c>
       <c r="E16">
-        <v>-1820.182</v>
+        <v>-1737.645</v>
       </c>
       <c r="F16">
-        <v>1155.518</v>
+        <v>1238.055</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2593,28 +2593,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M16">
-        <v>61.82021300000001</v>
+        <v>66.23594250000001</v>
       </c>
       <c r="N16">
-        <v>332.4655012857143</v>
+        <v>328.0497717857143</v>
       </c>
       <c r="O16">
-        <v>85.77609933171429</v>
+        <v>84.63684112071429</v>
       </c>
       <c r="P16">
-        <v>246.689401954</v>
+        <v>243.412930665</v>
       </c>
       <c r="Q16">
-        <v>586.689401954</v>
+        <v>583.412930665</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07327355074724662</v>
+        <v>0.07352236588721348</v>
       </c>
       <c r="T16">
-        <v>0.634493088850961</v>
+        <v>0.6402393969333366</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.377941698222784</v>
+        <v>5.952745585007932</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06844856100413145</v>
+        <v>0.06841926436563081</v>
       </c>
       <c r="C17">
-        <v>6689.394504126071</v>
+        <v>6609.847890700952</v>
       </c>
       <c r="D17">
-        <v>7927.449504126072</v>
+        <v>7930.439890700952</v>
       </c>
       <c r="E17">
-        <v>-1737.645</v>
+        <v>-1655.108</v>
       </c>
       <c r="F17">
-        <v>1238.055</v>
+        <v>1320.592</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2675,45 +2675,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M17">
-        <v>66.23594250000001</v>
+        <v>71.70814560000001</v>
       </c>
       <c r="N17">
-        <v>328.0497717857143</v>
+        <v>322.5775686857143</v>
       </c>
       <c r="O17">
-        <v>84.63684112071429</v>
+        <v>83.22501272091429</v>
       </c>
       <c r="P17">
-        <v>243.412930665</v>
+        <v>239.3525559648</v>
       </c>
       <c r="Q17">
-        <v>583.412930665</v>
+        <v>579.3525559648</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07352236588721348</v>
+        <v>0.07377710519717955</v>
       </c>
       <c r="T17">
-        <v>0.6402393969333366</v>
+        <v>0.6461225218748162</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>5.952745585007932</v>
+        <v>5.498478743058087</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06841926436563081</v>
+        <v>0.06830092772713017</v>
       </c>
       <c r="C18">
-        <v>6609.847890700952</v>
+        <v>6539.412825162177</v>
       </c>
       <c r="D18">
-        <v>7930.439890700952</v>
+        <v>7942.541825162177</v>
       </c>
       <c r="E18">
-        <v>-1655.108</v>
+        <v>-1572.571</v>
       </c>
       <c r="F18">
-        <v>1320.592</v>
+        <v>1403.129</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M18">
-        <v>71.70814560000001</v>
+        <v>76.18990470000001</v>
       </c>
       <c r="N18">
-        <v>322.5775686857143</v>
+        <v>318.0958095857143</v>
       </c>
       <c r="O18">
-        <v>83.22501272091429</v>
+        <v>82.06871887311431</v>
       </c>
       <c r="P18">
-        <v>239.3525559648</v>
+        <v>236.0270907126</v>
       </c>
       <c r="Q18">
-        <v>579.3525559648</v>
+        <v>576.0270907126001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07377710519717955</v>
+        <v>0.0740379828037713</v>
       </c>
       <c r="T18">
-        <v>0.6461225218748162</v>
+        <v>0.6521474088630786</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.498478743058087</v>
+        <v>5.175038816995847</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06830092772713017</v>
+        <v>0.06818259108862955</v>
       </c>
       <c r="C19">
-        <v>6539.412825162177</v>
+        <v>6469.014751431153</v>
       </c>
       <c r="D19">
-        <v>7942.541825162177</v>
+        <v>7954.680751431153</v>
       </c>
       <c r="E19">
-        <v>-1572.571</v>
+        <v>-1490.033999999999</v>
       </c>
       <c r="F19">
-        <v>1403.129</v>
+        <v>1485.666</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2839,28 +2839,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M19">
-        <v>76.18990470000001</v>
+        <v>80.67166380000002</v>
       </c>
       <c r="N19">
-        <v>318.0958095857143</v>
+        <v>313.6140504857143</v>
       </c>
       <c r="O19">
-        <v>82.06871887311431</v>
+        <v>80.91242502531429</v>
       </c>
       <c r="P19">
-        <v>236.0270907126</v>
+        <v>232.7016254604</v>
       </c>
       <c r="Q19">
-        <v>576.0270907126001</v>
+        <v>572.7016254604</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0740379828037713</v>
+        <v>0.07430522327881653</v>
       </c>
       <c r="T19">
-        <v>0.6521474088630786</v>
+        <v>0.6583192443144693</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.175038816995847</v>
+        <v>4.887536660496076</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06818259108862956</v>
+        <v>0.06806425445012891</v>
       </c>
       <c r="C20">
-        <v>6469.014751431152</v>
+        <v>6398.653839375987</v>
       </c>
       <c r="D20">
-        <v>7954.680751431152</v>
+        <v>7966.856839375987</v>
       </c>
       <c r="E20">
-        <v>-1490.034</v>
+        <v>-1407.497</v>
       </c>
       <c r="F20">
-        <v>1485.666</v>
+        <v>1568.203</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2921,28 +2921,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M20">
-        <v>80.6716638</v>
+        <v>85.15342290000001</v>
       </c>
       <c r="N20">
-        <v>313.6140504857143</v>
+        <v>309.1322913857143</v>
       </c>
       <c r="O20">
-        <v>80.91242502531429</v>
+        <v>79.75613117751429</v>
       </c>
       <c r="P20">
-        <v>232.7016254604</v>
+        <v>229.3761602082</v>
       </c>
       <c r="Q20">
-        <v>572.7016254604</v>
+        <v>569.3761602082</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07430522327881653</v>
+        <v>0.07457906228410977</v>
       </c>
       <c r="T20">
-        <v>0.6583192443144693</v>
+        <v>0.6646434707646599</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.887536660496077</v>
+        <v>4.63029788889102</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06806425445012891</v>
+        <v>0.06794591781162829</v>
       </c>
       <c r="C21">
-        <v>6398.653839375987</v>
+        <v>6328.330259906425</v>
       </c>
       <c r="D21">
-        <v>7966.856839375987</v>
+        <v>7979.070259906425</v>
       </c>
       <c r="E21">
-        <v>-1407.497</v>
+        <v>-1324.96</v>
       </c>
       <c r="F21">
-        <v>1568.203</v>
+        <v>1650.74</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3003,28 +3003,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M21">
-        <v>85.15342290000001</v>
+        <v>89.63518200000001</v>
       </c>
       <c r="N21">
-        <v>309.1322913857143</v>
+        <v>304.6505322857143</v>
       </c>
       <c r="O21">
-        <v>79.75613117751429</v>
+        <v>78.5998373297143</v>
       </c>
       <c r="P21">
-        <v>229.3761602082</v>
+        <v>226.050694956</v>
       </c>
       <c r="Q21">
-        <v>569.3761602082</v>
+        <v>566.050694956</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07457906228410977</v>
+        <v>0.07485974726453536</v>
       </c>
       <c r="T21">
-        <v>0.6646434707646599</v>
+        <v>0.6711258028761051</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.63029788889102</v>
+        <v>4.39878299444647</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06794591781162829</v>
+        <v>0.06798340117312765</v>
       </c>
       <c r="C22">
-        <v>6328.330259906425</v>
+        <v>6241.920584904483</v>
       </c>
       <c r="D22">
-        <v>7979.070259906425</v>
+        <v>7975.197584904483</v>
       </c>
       <c r="E22">
-        <v>-1324.96</v>
+        <v>-1242.423</v>
       </c>
       <c r="F22">
-        <v>1650.74</v>
+        <v>1733.277</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3085,45 +3085,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M22">
-        <v>89.63518200000001</v>
+        <v>95.85021810000002</v>
       </c>
       <c r="N22">
-        <v>304.6505322857143</v>
+        <v>298.4354961857143</v>
       </c>
       <c r="O22">
-        <v>78.5998373297143</v>
+        <v>76.9963580159143</v>
       </c>
       <c r="P22">
-        <v>226.050694956</v>
+        <v>221.4391381698</v>
       </c>
       <c r="Q22">
-        <v>566.050694956</v>
+        <v>561.4391381698</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07485974726453536</v>
+        <v>0.07514753819383246</v>
       </c>
       <c r="T22">
-        <v>0.6711258028761051</v>
+        <v>0.677772244661258</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.39878299444647</v>
+        <v>4.113560950631935</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06798340117312765</v>
+        <v>0.06787248453462702</v>
       </c>
       <c r="C23">
-        <v>6241.920584904483</v>
+        <v>6170.854090657542</v>
       </c>
       <c r="D23">
-        <v>7975.197584904483</v>
+        <v>7986.668090657542</v>
       </c>
       <c r="E23">
-        <v>-1242.423</v>
+        <v>-1159.886</v>
       </c>
       <c r="F23">
-        <v>1733.277</v>
+        <v>1815.814</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3167,28 +3167,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M23">
-        <v>95.85021810000001</v>
+        <v>100.4145142</v>
       </c>
       <c r="N23">
-        <v>298.4354961857143</v>
+        <v>293.8712000857143</v>
       </c>
       <c r="O23">
-        <v>76.9963580159143</v>
+        <v>75.8187696221143</v>
       </c>
       <c r="P23">
-        <v>221.4391381698</v>
+        <v>218.0524304636</v>
       </c>
       <c r="Q23">
-        <v>561.4391381698</v>
+        <v>558.0524304636001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07514753819383246</v>
+        <v>0.07544270837772694</v>
       </c>
       <c r="T23">
-        <v>0.6777722446612578</v>
+        <v>0.6845891080306453</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.113560950631935</v>
+        <v>3.926580907421393</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06787248453462702</v>
+        <v>0.06776156789612639</v>
       </c>
       <c r="C24">
-        <v>6170.854090657542</v>
+        <v>6099.82063935668</v>
       </c>
       <c r="D24">
-        <v>7986.668090657542</v>
+        <v>7998.17163935668</v>
       </c>
       <c r="E24">
-        <v>-1159.886</v>
+        <v>-1077.348999999999</v>
       </c>
       <c r="F24">
-        <v>1815.814</v>
+        <v>1898.351</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3249,28 +3249,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M24">
-        <v>100.4145142</v>
+        <v>104.9788103</v>
       </c>
       <c r="N24">
-        <v>293.8712000857143</v>
+        <v>289.3069039857143</v>
       </c>
       <c r="O24">
-        <v>75.8187696221143</v>
+        <v>74.6411812283143</v>
       </c>
       <c r="P24">
-        <v>218.0524304636</v>
+        <v>214.6657227574</v>
       </c>
       <c r="Q24">
-        <v>558.0524304636001</v>
+        <v>554.6657227574001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07544270837772694</v>
+        <v>0.07574554531964466</v>
       </c>
       <c r="T24">
-        <v>0.6845891080306453</v>
+        <v>0.6915830327862507</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.926580907421393</v>
+        <v>3.75585999840307</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06776156789612639</v>
+        <v>0.06765065125762575</v>
       </c>
       <c r="C25">
-        <v>6099.82063935668</v>
+        <v>6028.820373987464</v>
       </c>
       <c r="D25">
-        <v>7998.17163935668</v>
+        <v>8009.708373987465</v>
       </c>
       <c r="E25">
-        <v>-1077.348999999999</v>
+        <v>-994.8119999999994</v>
       </c>
       <c r="F25">
-        <v>1898.351</v>
+        <v>1980.888</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3331,28 +3331,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M25">
-        <v>104.9788103</v>
+        <v>109.5431064</v>
       </c>
       <c r="N25">
-        <v>289.3069039857143</v>
+        <v>284.7426078857143</v>
       </c>
       <c r="O25">
-        <v>74.6411812283143</v>
+        <v>73.46359283451429</v>
       </c>
       <c r="P25">
-        <v>214.6657227574</v>
+        <v>211.2790150512</v>
       </c>
       <c r="Q25">
-        <v>554.6657227574001</v>
+        <v>551.2790150512</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07574554531964466</v>
+        <v>0.07605635165477072</v>
       </c>
       <c r="T25">
-        <v>0.6915830327862507</v>
+        <v>0.6987610081933192</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.75585999840307</v>
+        <v>3.599365831802942</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06765065125762575</v>
+        <v>0.06753973461912512</v>
       </c>
       <c r="C26">
-        <v>6028.820373987465</v>
+        <v>5957.853438361633</v>
       </c>
       <c r="D26">
-        <v>8009.708373987465</v>
+        <v>8021.278438361634</v>
       </c>
       <c r="E26">
-        <v>-994.8119999999997</v>
+        <v>-912.2749999999996</v>
       </c>
       <c r="F26">
-        <v>1980.888</v>
+        <v>2063.425</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3413,28 +3413,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M26">
-        <v>109.5431064</v>
+        <v>114.1074025</v>
       </c>
       <c r="N26">
-        <v>284.7426078857143</v>
+        <v>280.1783117857143</v>
       </c>
       <c r="O26">
-        <v>73.4635928345143</v>
+        <v>72.28600444071429</v>
       </c>
       <c r="P26">
-        <v>211.2790150512</v>
+        <v>207.892307345</v>
       </c>
       <c r="Q26">
-        <v>551.2790150512001</v>
+        <v>547.8923073450001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07605635165477072</v>
+        <v>0.07637544615883349</v>
       </c>
       <c r="T26">
-        <v>0.6987610081933192</v>
+        <v>0.7061303962779096</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.599365831802943</v>
+        <v>3.455391198530825</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06753973461912512</v>
+        <v>0.06742881798062447</v>
       </c>
       <c r="C27">
-        <v>5957.853438361633</v>
+        <v>5886.919977123076</v>
       </c>
       <c r="D27">
-        <v>8021.278438361634</v>
+        <v>8032.881977123076</v>
       </c>
       <c r="E27">
-        <v>-912.2749999999996</v>
+        <v>-829.7379999999994</v>
       </c>
       <c r="F27">
-        <v>2063.425</v>
+        <v>2145.962</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3495,28 +3495,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M27">
-        <v>114.1074025</v>
+        <v>118.6716986</v>
       </c>
       <c r="N27">
-        <v>280.1783117857143</v>
+        <v>275.6140156857143</v>
       </c>
       <c r="O27">
-        <v>72.28600444071429</v>
+        <v>71.1084160469143</v>
       </c>
       <c r="P27">
-        <v>207.892307345</v>
+        <v>204.5055996388</v>
       </c>
       <c r="Q27">
-        <v>547.8923073450001</v>
+        <v>544.5055996388</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07637544615883349</v>
+        <v>0.07670316483868173</v>
       </c>
       <c r="T27">
-        <v>0.7061303962779096</v>
+        <v>0.7136989570134349</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.455391198530825</v>
+        <v>3.32249153704887</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06742881798062447</v>
+        <v>0.06731790134212386</v>
       </c>
       <c r="C28">
-        <v>5886.919977123076</v>
+        <v>5816.020135753855</v>
       </c>
       <c r="D28">
-        <v>8032.881977123076</v>
+        <v>8044.519135753855</v>
       </c>
       <c r="E28">
-        <v>-829.7379999999994</v>
+        <v>-747.2009999999996</v>
       </c>
       <c r="F28">
-        <v>2145.962</v>
+        <v>2228.499</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3577,28 +3577,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M28">
-        <v>118.6716986</v>
+        <v>123.2359947</v>
       </c>
       <c r="N28">
-        <v>275.6140156857143</v>
+        <v>271.0497195857143</v>
       </c>
       <c r="O28">
-        <v>71.1084160469143</v>
+        <v>69.93082765311431</v>
       </c>
       <c r="P28">
-        <v>204.5055996388</v>
+        <v>201.1188919326</v>
       </c>
       <c r="Q28">
-        <v>544.5055996388</v>
+        <v>541.1188919326</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07670316483868173</v>
+        <v>0.07703986211249843</v>
       </c>
       <c r="T28">
-        <v>0.7136989570134349</v>
+        <v>0.7214748755773308</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.32249153704887</v>
+        <v>3.199436294935949</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06731790134212386</v>
+        <v>0.06720698470362321</v>
       </c>
       <c r="C29">
-        <v>5816.020135753855</v>
+        <v>5745.1540605803</v>
       </c>
       <c r="D29">
-        <v>8044.519135753855</v>
+        <v>8056.1900605803</v>
       </c>
       <c r="E29">
-        <v>-747.2009999999996</v>
+        <v>-664.6639999999993</v>
       </c>
       <c r="F29">
-        <v>2228.499</v>
+        <v>2311.036000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3659,28 +3659,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M29">
-        <v>123.2359947</v>
+        <v>127.8002908</v>
       </c>
       <c r="N29">
-        <v>271.0497195857143</v>
+        <v>266.4854234857143</v>
       </c>
       <c r="O29">
-        <v>69.93082765311431</v>
+        <v>68.7532392593143</v>
       </c>
       <c r="P29">
-        <v>201.1188919326</v>
+        <v>197.7321842264</v>
       </c>
       <c r="Q29">
-        <v>541.1188919326</v>
+        <v>537.7321842264</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07703986211249843</v>
+        <v>0.07738591208836558</v>
       </c>
       <c r="T29">
-        <v>0.7214748755773308</v>
+        <v>0.7294667918791127</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.199436294935949</v>
+        <v>3.085170712973951</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06720698470362321</v>
+        <v>0.06763401806512258</v>
       </c>
       <c r="C30">
-        <v>5745.1540605803</v>
+        <v>5617.868306912765</v>
       </c>
       <c r="D30">
-        <v>8056.1900605803</v>
+        <v>8011.441306912765</v>
       </c>
       <c r="E30">
-        <v>-664.6639999999993</v>
+        <v>-582.1269999999995</v>
       </c>
       <c r="F30">
-        <v>2311.036000000001</v>
+        <v>2393.573</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3741,45 +3741,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M30">
-        <v>127.8002908</v>
+        <v>138.3485194</v>
       </c>
       <c r="N30">
-        <v>266.4854234857143</v>
+        <v>255.9371948857143</v>
       </c>
       <c r="O30">
-        <v>68.7532392593143</v>
+        <v>66.0317962805143</v>
       </c>
       <c r="P30">
-        <v>197.7321842264</v>
+        <v>189.9053986052</v>
       </c>
       <c r="Q30">
-        <v>537.7321842264</v>
+        <v>529.9053986052</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07738591208836558</v>
+        <v>0.07774170995087687</v>
       </c>
       <c r="T30">
-        <v>0.7294667918791127</v>
+        <v>0.7376838325837615</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.085170712973951</v>
+        <v>2.849945311996699</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06763401806512258</v>
+        <v>0.06754165142662194</v>
       </c>
       <c r="C31">
-        <v>5617.868306912766</v>
+        <v>5544.968206298556</v>
       </c>
       <c r="D31">
-        <v>8011.441306912765</v>
+        <v>8021.078206298555</v>
       </c>
       <c r="E31">
-        <v>-582.127</v>
+        <v>-499.5899999999997</v>
       </c>
       <c r="F31">
-        <v>2393.573</v>
+        <v>2476.11</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3823,28 +3823,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M31">
-        <v>138.3485194</v>
+        <v>143.119158</v>
       </c>
       <c r="N31">
-        <v>255.9371948857143</v>
+        <v>251.1665562857143</v>
       </c>
       <c r="O31">
-        <v>66.0317962805143</v>
+        <v>64.80097152171429</v>
       </c>
       <c r="P31">
-        <v>189.9053986052</v>
+        <v>186.365584764</v>
       </c>
       <c r="Q31">
-        <v>529.9053986052</v>
+        <v>526.365584764</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07774170995087687</v>
+        <v>0.07810767346660277</v>
       </c>
       <c r="T31">
-        <v>0.7376838325837615</v>
+        <v>0.7461356458799718</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.849945311996699</v>
+        <v>2.754947134930141</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06754165142662194</v>
+        <v>0.0674492847881213</v>
       </c>
       <c r="C32">
-        <v>5544.968206298556</v>
+        <v>5472.09131790625</v>
       </c>
       <c r="D32">
-        <v>8021.078206298555</v>
+        <v>8030.738317906251</v>
       </c>
       <c r="E32">
-        <v>-499.5899999999997</v>
+        <v>-417.0529999999994</v>
       </c>
       <c r="F32">
-        <v>2476.11</v>
+        <v>2558.647</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3905,28 +3905,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M32">
-        <v>143.119158</v>
+        <v>147.8897966</v>
       </c>
       <c r="N32">
-        <v>251.1665562857143</v>
+        <v>246.3959176857143</v>
       </c>
       <c r="O32">
-        <v>64.80097152171429</v>
+        <v>63.57014676291429</v>
       </c>
       <c r="P32">
-        <v>186.365584764</v>
+        <v>182.8257709228</v>
       </c>
       <c r="Q32">
-        <v>526.365584764</v>
+        <v>522.8257709228001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07810767346660277</v>
+        <v>0.07848424462046567</v>
       </c>
       <c r="T32">
-        <v>0.7461356458799718</v>
+        <v>0.7548324392717246</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.754947134930141</v>
+        <v>2.66607787251304</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0674492847881213</v>
+        <v>0.06735691814962068</v>
       </c>
       <c r="C33">
-        <v>5472.09131790625</v>
+        <v>5399.237725703251</v>
       </c>
       <c r="D33">
-        <v>8030.738317906251</v>
+        <v>8040.421725703251</v>
       </c>
       <c r="E33">
-        <v>-417.0529999999994</v>
+        <v>-334.5159999999996</v>
       </c>
       <c r="F33">
-        <v>2558.647</v>
+        <v>2641.184</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3987,28 +3987,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M33">
-        <v>147.8897966</v>
+        <v>152.6604352</v>
       </c>
       <c r="N33">
-        <v>246.3959176857143</v>
+        <v>241.6252790857143</v>
       </c>
       <c r="O33">
-        <v>63.57014676291429</v>
+        <v>62.33932200411429</v>
       </c>
       <c r="P33">
-        <v>182.8257709228</v>
+        <v>179.2859570816</v>
       </c>
       <c r="Q33">
-        <v>522.8257709228001</v>
+        <v>519.2859570816</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07848424462046567</v>
+        <v>0.078871891396501</v>
       </c>
       <c r="T33">
-        <v>0.7548324392717246</v>
+        <v>0.7637850207044111</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.66607787251304</v>
+        <v>2.582762938997008</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06735691814962068</v>
+        <v>0.06726455151112004</v>
       </c>
       <c r="C34">
-        <v>5399.237725703251</v>
+        <v>5326.407514062437</v>
       </c>
       <c r="D34">
-        <v>8040.421725703251</v>
+        <v>8050.128514062438</v>
       </c>
       <c r="E34">
-        <v>-334.5159999999996</v>
+        <v>-251.9789999999994</v>
       </c>
       <c r="F34">
-        <v>2641.184</v>
+        <v>2723.721</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4069,28 +4069,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M34">
-        <v>152.6604352</v>
+        <v>157.4310738</v>
       </c>
       <c r="N34">
-        <v>241.6252790857143</v>
+        <v>236.8546404857143</v>
       </c>
       <c r="O34">
-        <v>62.33932200411429</v>
+        <v>61.10849724531429</v>
       </c>
       <c r="P34">
-        <v>179.2859570816</v>
+        <v>175.7461432404</v>
       </c>
       <c r="Q34">
-        <v>519.2859570816</v>
+        <v>515.7461432404</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.078871891396501</v>
+        <v>0.07927110971808962</v>
       </c>
       <c r="T34">
-        <v>0.7637850207044111</v>
+        <v>0.7730048433738942</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.582762938997008</v>
+        <v>2.504497395391038</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06726455151112004</v>
+        <v>0.06805516487261941</v>
       </c>
       <c r="C35">
-        <v>5326.407514062437</v>
+        <v>5161.535640856113</v>
       </c>
       <c r="D35">
-        <v>8050.128514062438</v>
+        <v>7967.793640856113</v>
       </c>
       <c r="E35">
-        <v>-251.9789999999994</v>
+        <v>-169.4419999999996</v>
       </c>
       <c r="F35">
-        <v>2723.721</v>
+        <v>2806.258</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4151,45 +4151,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M35">
-        <v>157.4310738</v>
+        <v>172.0236154</v>
       </c>
       <c r="N35">
-        <v>236.8546404857143</v>
+        <v>222.2620988857143</v>
       </c>
       <c r="O35">
-        <v>61.10849724531429</v>
+        <v>57.3436215125143</v>
       </c>
       <c r="P35">
-        <v>175.7461432404</v>
+        <v>164.9184773732</v>
       </c>
       <c r="Q35">
-        <v>515.7461432404</v>
+        <v>504.9184773732001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07927110971808962</v>
+        <v>0.07968242556457486</v>
       </c>
       <c r="T35">
-        <v>0.7730048433738942</v>
+        <v>0.7825040546091193</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.504497395391038</v>
+        <v>2.292044108995714</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06805516487261941</v>
+        <v>0.06871592823411878</v>
       </c>
       <c r="C36">
-        <v>5161.535640856113</v>
+        <v>5011.467461967615</v>
       </c>
       <c r="D36">
-        <v>7967.793640856113</v>
+        <v>7900.262461967616</v>
       </c>
       <c r="E36">
-        <v>-169.4419999999996</v>
+        <v>-86.90499999999929</v>
       </c>
       <c r="F36">
-        <v>2806.258</v>
+        <v>2888.795000000001</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4233,45 +4233,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M36">
-        <v>172.0236154</v>
+        <v>185.1717595</v>
       </c>
       <c r="N36">
-        <v>222.2620988857143</v>
+        <v>209.1139547857143</v>
       </c>
       <c r="O36">
-        <v>57.3436215125143</v>
+        <v>53.95140033471429</v>
       </c>
       <c r="P36">
-        <v>164.9184773732</v>
+        <v>155.162554451</v>
       </c>
       <c r="Q36">
-        <v>504.9184773732001</v>
+        <v>495.162554451</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07968242556457486</v>
+        <v>0.08010639728325966</v>
       </c>
       <c r="T36">
-        <v>0.7825040546091193</v>
+        <v>0.7922955492669668</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.292044108995714</v>
+        <v>2.129297228423831</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06871592823411878</v>
+        <v>0.06867030759561815</v>
       </c>
       <c r="C37">
-        <v>5011.467461967615</v>
+        <v>4933.556161176155</v>
       </c>
       <c r="D37">
-        <v>7900.262461967616</v>
+        <v>7904.888161176156</v>
       </c>
       <c r="E37">
-        <v>-86.90499999999929</v>
+        <v>-4.367999999999029</v>
       </c>
       <c r="F37">
-        <v>2888.795000000001</v>
+        <v>2971.332000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4315,28 +4315,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M37">
-        <v>185.1717595</v>
+        <v>190.4623812000001</v>
       </c>
       <c r="N37">
-        <v>209.1139547857143</v>
+        <v>203.8233330857143</v>
       </c>
       <c r="O37">
-        <v>53.95140033471429</v>
+        <v>52.58641993611428</v>
       </c>
       <c r="P37">
-        <v>155.162554451</v>
+        <v>151.2369131496</v>
       </c>
       <c r="Q37">
-        <v>495.162554451</v>
+        <v>491.2369131496</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08010639728325966</v>
+        <v>0.08054361811815336</v>
       </c>
       <c r="T37">
-        <v>0.7922955492669668</v>
+        <v>0.8023930281328718</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.129297228423831</v>
+        <v>2.070150083189835</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06867030759561815</v>
+        <v>0.06862468695711751</v>
       </c>
       <c r="C38">
-        <v>4933.556161176156</v>
+        <v>4855.65028036381</v>
       </c>
       <c r="D38">
-        <v>7904.888161176156</v>
+        <v>7909.51928036381</v>
       </c>
       <c r="E38">
-        <v>-4.367999999999483</v>
+        <v>78.16900000000032</v>
       </c>
       <c r="F38">
-        <v>2971.332</v>
+        <v>3053.869</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4397,28 +4397,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M38">
-        <v>190.4623812</v>
+        <v>195.7530029</v>
       </c>
       <c r="N38">
-        <v>203.8233330857143</v>
+        <v>198.5327113857143</v>
       </c>
       <c r="O38">
-        <v>52.58641993611429</v>
+        <v>51.2214395375143</v>
       </c>
       <c r="P38">
-        <v>151.2369131496</v>
+        <v>147.3112718482</v>
       </c>
       <c r="Q38">
-        <v>491.2369131496</v>
+        <v>487.3112718482</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08054361811815336</v>
+        <v>0.0809947189795516</v>
       </c>
       <c r="T38">
-        <v>0.8023930281328718</v>
+        <v>0.8128110618834089</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.070150083189836</v>
+        <v>2.014200080941462</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06862468695711751</v>
+        <v>0.07187799831861688</v>
       </c>
       <c r="C39">
-        <v>4855.65028036381</v>
+        <v>4455.916236496905</v>
       </c>
       <c r="D39">
-        <v>7909.51928036381</v>
+        <v>7592.322236496905</v>
       </c>
       <c r="E39">
-        <v>78.16900000000032</v>
+        <v>160.7060000000006</v>
       </c>
       <c r="F39">
-        <v>3053.869</v>
+        <v>3136.406</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4479,45 +4479,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M39">
-        <v>195.7530029</v>
+        <v>237.7395748</v>
       </c>
       <c r="N39">
-        <v>198.5327113857143</v>
+        <v>156.5461394857143</v>
       </c>
       <c r="O39">
-        <v>51.2214395375143</v>
+        <v>40.38890398731429</v>
       </c>
       <c r="P39">
-        <v>147.3112718482</v>
+        <v>116.1572354984</v>
       </c>
       <c r="Q39">
-        <v>487.3112718482</v>
+        <v>456.1572354984</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0809947189795516</v>
+        <v>0.08146037148164012</v>
       </c>
       <c r="T39">
-        <v>0.8128110618834089</v>
+        <v>0.823565161238802</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.04756220000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.014200080941462</v>
+        <v>1.658477410071124</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07187799831861688</v>
+        <v>0.07191919168011623</v>
       </c>
       <c r="C40">
-        <v>4455.916236496905</v>
+        <v>4369.525918905804</v>
       </c>
       <c r="D40">
-        <v>7592.322236496905</v>
+        <v>7588.468918905804</v>
       </c>
       <c r="E40">
-        <v>160.7060000000006</v>
+        <v>243.2430000000004</v>
       </c>
       <c r="F40">
-        <v>3136.406</v>
+        <v>3218.943</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4561,28 +4561,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M40">
-        <v>237.7395748</v>
+        <v>243.9958794</v>
       </c>
       <c r="N40">
-        <v>156.5461394857143</v>
+        <v>150.2898348857143</v>
       </c>
       <c r="O40">
-        <v>40.38890398731429</v>
+        <v>38.77477740051429</v>
       </c>
       <c r="P40">
-        <v>116.1572354984</v>
+        <v>111.5150574852</v>
       </c>
       <c r="Q40">
-        <v>456.1572354984</v>
+        <v>451.5150574852</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08146037148164012</v>
+        <v>0.08194129127887909</v>
       </c>
       <c r="T40">
-        <v>0.823565161238802</v>
+        <v>0.8346718540156833</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.658477410071124</v>
+        <v>1.615952348274428</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07191919168011623</v>
+        <v>0.07196038504161562</v>
       </c>
       <c r="C41">
-        <v>4369.525918905804</v>
+        <v>4283.139510665228</v>
       </c>
       <c r="D41">
-        <v>7588.468918905804</v>
+        <v>7584.619510665229</v>
       </c>
       <c r="E41">
-        <v>243.2430000000004</v>
+        <v>325.7800000000007</v>
       </c>
       <c r="F41">
-        <v>3218.943</v>
+        <v>3301.48</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4643,28 +4643,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M41">
-        <v>243.9958794</v>
+        <v>250.2521840000001</v>
       </c>
       <c r="N41">
-        <v>150.2898348857143</v>
+        <v>144.0335302857143</v>
       </c>
       <c r="O41">
-        <v>38.77477740051429</v>
+        <v>37.16065081371428</v>
       </c>
       <c r="P41">
-        <v>111.5150574852</v>
+        <v>106.872879472</v>
       </c>
       <c r="Q41">
-        <v>451.5150574852</v>
+        <v>446.872879472</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08194129127887909</v>
+        <v>0.08243824173602601</v>
       </c>
       <c r="T41">
-        <v>0.8346718540156833</v>
+        <v>0.8461487698851274</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.615952348274428</v>
+        <v>1.575553539567568</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07196038504161562</v>
+        <v>0.07200157840311498</v>
       </c>
       <c r="C42">
-        <v>4283.139510665228</v>
+        <v>4196.7570058289</v>
       </c>
       <c r="D42">
-        <v>7584.619510665229</v>
+        <v>7580.774005828901</v>
       </c>
       <c r="E42">
-        <v>325.7800000000007</v>
+        <v>408.3170000000009</v>
       </c>
       <c r="F42">
-        <v>3301.48</v>
+        <v>3384.017000000001</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4725,28 +4725,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M42">
-        <v>250.2521840000001</v>
+        <v>256.5084886000001</v>
       </c>
       <c r="N42">
-        <v>144.0335302857143</v>
+        <v>137.7772256857143</v>
       </c>
       <c r="O42">
-        <v>37.16065081371428</v>
+        <v>35.54652422691428</v>
       </c>
       <c r="P42">
-        <v>106.872879472</v>
+        <v>102.2307014588</v>
       </c>
       <c r="Q42">
-        <v>446.872879472</v>
+        <v>442.2307014588</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08243824173602601</v>
+        <v>0.08295203797138131</v>
       </c>
       <c r="T42">
-        <v>0.8461487698851274</v>
+        <v>0.8580147337501458</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.575553539567568</v>
+        <v>1.537125404456164</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07200157840311498</v>
+        <v>0.07204277176461435</v>
       </c>
       <c r="C43">
-        <v>4196.7570058289</v>
+        <v>4110.378398462593</v>
       </c>
       <c r="D43">
-        <v>7580.774005828901</v>
+        <v>7576.932398462594</v>
       </c>
       <c r="E43">
-        <v>408.3170000000009</v>
+        <v>490.8540000000007</v>
       </c>
       <c r="F43">
-        <v>3384.017000000001</v>
+        <v>3466.554000000001</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4807,28 +4807,28 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M43">
-        <v>256.5084886000001</v>
+        <v>262.7647932</v>
       </c>
       <c r="N43">
-        <v>137.7772256857143</v>
+        <v>131.5209210857143</v>
       </c>
       <c r="O43">
-        <v>35.54652422691428</v>
+        <v>33.93239764011429</v>
       </c>
       <c r="P43">
-        <v>102.2307014588</v>
+        <v>97.5885234456</v>
       </c>
       <c r="Q43">
-        <v>442.2307014588</v>
+        <v>437.5885234456</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08295203797138131</v>
+        <v>0.0834835513183006</v>
       </c>
       <c r="T43">
-        <v>0.8580147337501458</v>
+        <v>0.8702898687829236</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.537125404456164</v>
+        <v>1.500527180540541</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07204277176461435</v>
+        <v>0.08674444415094613</v>
       </c>
       <c r="C44">
-        <v>4110.378398462594</v>
+        <v>2867.369884637179</v>
       </c>
       <c r="D44">
-        <v>7576.932398462594</v>
+        <v>6416.460884637179</v>
       </c>
       <c r="E44">
-        <v>490.8540000000003</v>
+        <v>573.3910000000005</v>
       </c>
       <c r="F44">
-        <v>3466.554</v>
+        <v>3549.091</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4889,45 +4889,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M44">
-        <v>262.7647932</v>
+        <v>420.9221926000001</v>
       </c>
       <c r="N44">
-        <v>131.5209210857143</v>
+        <v>-26.63647831428574</v>
       </c>
       <c r="O44">
-        <v>33.93239764011429</v>
+        <v>-6.872211405085721</v>
       </c>
       <c r="P44">
-        <v>97.5885234456</v>
+        <v>-19.76426690920002</v>
       </c>
       <c r="Q44">
-        <v>437.5885234456</v>
+        <v>320.2357330908</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0834835513183006</v>
+        <v>0.08433562499548386</v>
       </c>
       <c r="T44">
-        <v>0.8702898687829236</v>
+        <v>0.8899682446993964</v>
       </c>
       <c r="U44">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V44">
-        <v>0.258</v>
+        <v>0.2416734400658785</v>
       </c>
       <c r="W44">
-        <v>0.0562436</v>
+        <v>0.08993753000818681</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.500527180540541</v>
+        <v>0.9367187599452657</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08674444415094613</v>
+        <v>0.08747244415094613</v>
       </c>
       <c r="C45">
-        <v>2867.369884637179</v>
+        <v>2736.5359081708</v>
       </c>
       <c r="D45">
-        <v>6416.460884637179</v>
+        <v>6368.1639081708</v>
       </c>
       <c r="E45">
-        <v>573.3910000000005</v>
+        <v>655.9280000000003</v>
       </c>
       <c r="F45">
-        <v>3549.091</v>
+        <v>3631.628</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4971,37 +4971,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M45">
-        <v>420.9221926000001</v>
+        <v>430.7110808</v>
       </c>
       <c r="N45">
-        <v>-26.63647831428574</v>
+        <v>-36.42536651428571</v>
       </c>
       <c r="O45">
-        <v>-6.872211405085721</v>
+        <v>-9.397744560685714</v>
       </c>
       <c r="P45">
-        <v>-19.76426690920002</v>
+        <v>-27.0276219536</v>
       </c>
       <c r="Q45">
-        <v>320.2357330908</v>
+        <v>312.9723780464</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08433562499548386</v>
+        <v>0.08502376115611751</v>
       </c>
       <c r="T45">
-        <v>0.8899682446993964</v>
+        <v>0.9058605347833142</v>
       </c>
       <c r="U45">
         <v>0.1186</v>
       </c>
       <c r="V45">
-        <v>0.2416734400658785</v>
+        <v>0.2361808618825631</v>
       </c>
       <c r="W45">
-        <v>0.08993753000818681</v>
+        <v>0.09058894978072801</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.9367187599452657</v>
+        <v>0.9154296972192369</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08747244415094613</v>
+        <v>0.08820044415094613</v>
       </c>
       <c r="C46">
-        <v>2736.5359081708</v>
+        <v>2606.423566755852</v>
       </c>
       <c r="D46">
-        <v>6368.1639081708</v>
+        <v>6320.588566755852</v>
       </c>
       <c r="E46">
-        <v>655.9280000000003</v>
+        <v>738.4650000000006</v>
       </c>
       <c r="F46">
-        <v>3631.628</v>
+        <v>3714.165</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5053,37 +5053,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M46">
-        <v>430.7110808</v>
+        <v>440.4999690000001</v>
       </c>
       <c r="N46">
-        <v>-36.42536651428571</v>
+        <v>-46.21425471428574</v>
       </c>
       <c r="O46">
-        <v>-9.397744560685714</v>
+        <v>-11.92327771628572</v>
       </c>
       <c r="P46">
-        <v>-27.0276219536</v>
+        <v>-34.29097699800002</v>
       </c>
       <c r="Q46">
-        <v>312.9723780464</v>
+        <v>305.709023002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08502376115611751</v>
+        <v>0.0857369204498651</v>
       </c>
       <c r="T46">
-        <v>0.9058605347833142</v>
+        <v>0.922330726324829</v>
       </c>
       <c r="U46">
         <v>0.1186</v>
       </c>
       <c r="V46">
-        <v>0.2361808618825631</v>
+        <v>0.2309323982851728</v>
       </c>
       <c r="W46">
-        <v>0.09058894978072801</v>
+        <v>0.0912114175633785</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.9154296972192369</v>
+        <v>0.8950868150588094</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08820044415094613</v>
+        <v>0.08892844415094614</v>
       </c>
       <c r="C47">
-        <v>2606.423566755852</v>
+        <v>2477.016806731511</v>
       </c>
       <c r="D47">
-        <v>6320.588566755852</v>
+        <v>6273.718806731512</v>
       </c>
       <c r="E47">
-        <v>738.4650000000006</v>
+        <v>821.0020000000009</v>
       </c>
       <c r="F47">
-        <v>3714.165</v>
+        <v>3796.702000000001</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5135,37 +5135,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M47">
-        <v>440.4999690000001</v>
+        <v>450.2888572000001</v>
       </c>
       <c r="N47">
-        <v>-46.21425471428574</v>
+        <v>-56.00314291428577</v>
       </c>
       <c r="O47">
-        <v>-11.92327771628572</v>
+        <v>-14.44881087188573</v>
       </c>
       <c r="P47">
-        <v>-34.29097699800002</v>
+        <v>-41.55433204240005</v>
       </c>
       <c r="Q47">
-        <v>305.709023002</v>
+        <v>298.4456679575999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0857369204498651</v>
+        <v>0.08647649305078853</v>
       </c>
       <c r="T47">
-        <v>0.922330726324829</v>
+        <v>0.9394109249604741</v>
       </c>
       <c r="U47">
         <v>0.1186</v>
       </c>
       <c r="V47">
-        <v>0.2309323982851728</v>
+        <v>0.2259121287572343</v>
       </c>
       <c r="W47">
-        <v>0.0912114175633785</v>
+        <v>0.09180682152939201</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8950868150588094</v>
+        <v>0.8756284060357917</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08892844415094614</v>
+        <v>0.08965644415094615</v>
       </c>
       <c r="C48">
-        <v>2477.016806731511</v>
+        <v>2348.300047109843</v>
       </c>
       <c r="D48">
-        <v>6273.718806731512</v>
+        <v>6227.539047109844</v>
       </c>
       <c r="E48">
-        <v>821.0020000000009</v>
+        <v>903.5390000000007</v>
       </c>
       <c r="F48">
-        <v>3796.702000000001</v>
+        <v>3879.239</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5217,37 +5217,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M48">
-        <v>450.2888572000001</v>
+        <v>460.0777454000001</v>
       </c>
       <c r="N48">
-        <v>-56.00314291428577</v>
+        <v>-65.79203111428575</v>
       </c>
       <c r="O48">
-        <v>-14.44881087188573</v>
+        <v>-16.97434402748572</v>
       </c>
       <c r="P48">
-        <v>-41.55433204240005</v>
+        <v>-48.81768708680002</v>
       </c>
       <c r="Q48">
-        <v>298.4456679575999</v>
+        <v>291.1823129132</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08647649305078853</v>
+        <v>0.0872439740517468</v>
       </c>
       <c r="T48">
-        <v>0.9394109249604741</v>
+        <v>0.9571356593936906</v>
       </c>
       <c r="U48">
         <v>0.1186</v>
       </c>
       <c r="V48">
-        <v>0.2259121287572343</v>
+        <v>0.2211054877198463</v>
       </c>
       <c r="W48">
-        <v>0.09180682152939201</v>
+        <v>0.09237688915642624</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8756284060357917</v>
+        <v>0.8569980144180089</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08965644415094615</v>
+        <v>0.09038444415094614</v>
       </c>
       <c r="C49">
-        <v>2348.300047109843</v>
+        <v>2220.258162306601</v>
       </c>
       <c r="D49">
-        <v>6227.539047109844</v>
+        <v>6182.034162306602</v>
       </c>
       <c r="E49">
-        <v>903.5390000000007</v>
+        <v>986.0760000000009</v>
       </c>
       <c r="F49">
-        <v>3879.239</v>
+        <v>3961.776000000001</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5299,37 +5299,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M49">
-        <v>460.0777454000001</v>
+        <v>469.8666336000001</v>
       </c>
       <c r="N49">
-        <v>-65.79203111428575</v>
+        <v>-75.58091931428578</v>
       </c>
       <c r="O49">
-        <v>-16.97434402748572</v>
+        <v>-19.49987718308573</v>
       </c>
       <c r="P49">
-        <v>-48.81768708680002</v>
+        <v>-56.08104213120005</v>
       </c>
       <c r="Q49">
-        <v>291.1823129132</v>
+        <v>283.9189578688</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.0872439740517468</v>
+        <v>0.08804097355274193</v>
       </c>
       <c r="T49">
-        <v>0.9571356593936906</v>
+        <v>0.9755421143820308</v>
       </c>
       <c r="U49">
         <v>0.1186</v>
       </c>
       <c r="V49">
-        <v>0.2211054877198463</v>
+        <v>0.2164991233923495</v>
       </c>
       <c r="W49">
-        <v>0.09237688915642624</v>
+        <v>0.09292320396566736</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8569980144180089</v>
+        <v>0.8391438891176337</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09038444415094612</v>
+        <v>0.09111244415094613</v>
       </c>
       <c r="C50">
-        <v>2220.258162306601</v>
+        <v>2092.876465623649</v>
       </c>
       <c r="D50">
-        <v>6182.034162306602</v>
+        <v>6137.189465623649</v>
       </c>
       <c r="E50">
-        <v>986.0760000000005</v>
+        <v>1068.613</v>
       </c>
       <c r="F50">
-        <v>3961.776</v>
+        <v>4044.313</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5381,37 +5381,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M50">
-        <v>469.8666336000001</v>
+        <v>479.6555218</v>
       </c>
       <c r="N50">
-        <v>-75.58091931428572</v>
+        <v>-85.3698075142857</v>
       </c>
       <c r="O50">
-        <v>-19.49987718308572</v>
+        <v>-22.02541033868571</v>
       </c>
       <c r="P50">
-        <v>-56.08104213120001</v>
+        <v>-63.34439717559999</v>
       </c>
       <c r="Q50">
-        <v>283.9189578688</v>
+        <v>276.6556028244</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08804097355274193</v>
+        <v>0.08886922793612902</v>
       </c>
       <c r="T50">
-        <v>0.9755421143820308</v>
+        <v>0.9946703911346194</v>
       </c>
       <c r="U50">
         <v>0.1186</v>
       </c>
       <c r="V50">
-        <v>0.2164991233923495</v>
+        <v>0.2120807739353628</v>
       </c>
       <c r="W50">
-        <v>0.09292320396566735</v>
+        <v>0.09344722021126597</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8391438891176338</v>
+        <v>0.8220185036254373</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09111244415094613</v>
+        <v>0.09184044415094614</v>
       </c>
       <c r="C51">
-        <v>2092.876465623649</v>
+        <v>1966.140693445132</v>
       </c>
       <c r="D51">
-        <v>6137.189465623649</v>
+        <v>6092.990693445133</v>
       </c>
       <c r="E51">
-        <v>1068.613</v>
+        <v>1151.150000000001</v>
       </c>
       <c r="F51">
-        <v>4044.313</v>
+        <v>4126.85</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5463,37 +5463,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M51">
-        <v>479.6555218</v>
+        <v>489.4444100000001</v>
       </c>
       <c r="N51">
-        <v>-85.3698075142857</v>
+        <v>-95.15869571428573</v>
       </c>
       <c r="O51">
-        <v>-22.02541033868571</v>
+        <v>-24.55094349428572</v>
       </c>
       <c r="P51">
-        <v>-63.34439717559999</v>
+        <v>-70.60775222000001</v>
       </c>
       <c r="Q51">
-        <v>276.6556028244</v>
+        <v>269.39224778</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08886922793612902</v>
+        <v>0.08973061249485161</v>
       </c>
       <c r="T51">
-        <v>0.9946703911346194</v>
+        <v>1.014563798957312</v>
       </c>
       <c r="U51">
         <v>0.1186</v>
       </c>
       <c r="V51">
-        <v>0.2120807739353628</v>
+        <v>0.2078391584566556</v>
       </c>
       <c r="W51">
-        <v>0.09344722021126597</v>
+        <v>0.09395027580704066</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8220185036254373</v>
+        <v>0.8055781335529285</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09184044415094614</v>
+        <v>0.1355332315228211</v>
       </c>
       <c r="C52">
-        <v>1966.140693445132</v>
+        <v>44.79924664825649</v>
       </c>
       <c r="D52">
-        <v>6092.990693445133</v>
+        <v>4254.186246648257</v>
       </c>
       <c r="E52">
-        <v>1151.150000000001</v>
+        <v>1233.687000000001</v>
       </c>
       <c r="F52">
-        <v>4126.85</v>
+        <v>4209.387000000001</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5545,45 +5545,45 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M52">
-        <v>489.4444100000001</v>
+        <v>845.2449096000001</v>
       </c>
       <c r="N52">
-        <v>-95.15869571428573</v>
+        <v>-450.9591953142858</v>
       </c>
       <c r="O52">
-        <v>-24.55094349428572</v>
+        <v>-116.3474723910857</v>
       </c>
       <c r="P52">
-        <v>-70.60775222000001</v>
+        <v>-334.6117229232001</v>
       </c>
       <c r="Q52">
-        <v>269.39224778</v>
+        <v>5.388277076799909</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08973061249485161</v>
+        <v>0.09275529310061374</v>
       </c>
       <c r="T52">
-        <v>1.014563798957312</v>
+        <v>1.084417854517638</v>
       </c>
       <c r="U52">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.2078391584566556</v>
+        <v>0.1203505790219482</v>
       </c>
       <c r="W52">
-        <v>0.09395027580704066</v>
+        <v>0.1766336037323928</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8055781335529285</v>
+        <v>0.4664751124881714</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1355332315228211</v>
+        <v>0.1370832315228211</v>
       </c>
       <c r="C53">
-        <v>44.79924664825649</v>
+        <v>-82.80060131111259</v>
       </c>
       <c r="D53">
-        <v>4254.186246648257</v>
+        <v>4209.123398688888</v>
       </c>
       <c r="E53">
-        <v>1233.687000000001</v>
+        <v>1316.224000000001</v>
       </c>
       <c r="F53">
-        <v>4209.387000000001</v>
+        <v>4291.924000000001</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5627,37 +5627,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M53">
-        <v>845.2449096000001</v>
+        <v>861.8183392000002</v>
       </c>
       <c r="N53">
-        <v>-450.9591953142858</v>
+        <v>-467.5326249142859</v>
       </c>
       <c r="O53">
-        <v>-116.3474723910857</v>
+        <v>-120.6234172278858</v>
       </c>
       <c r="P53">
-        <v>-334.6117229232001</v>
+        <v>-346.9092076864001</v>
       </c>
       <c r="Q53">
-        <v>5.388277076799909</v>
+        <v>-6.909207686400123</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09275529310061374</v>
+        <v>0.09373352837354319</v>
       </c>
       <c r="T53">
-        <v>1.084417854517638</v>
+        <v>1.107009893153422</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1203505790219482</v>
+        <v>0.1180361448099877</v>
       </c>
       <c r="W53">
-        <v>0.1766336037323928</v>
+        <v>0.1770983421221545</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4664751124881714</v>
+        <v>0.4575044372480143</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1370832315228211</v>
+        <v>0.1386332315228211</v>
       </c>
       <c r="C54">
-        <v>-82.80060131111259</v>
+        <v>-209.4557911585562</v>
       </c>
       <c r="D54">
-        <v>4209.123398688888</v>
+        <v>4165.005208841444</v>
       </c>
       <c r="E54">
-        <v>1316.224000000001</v>
+        <v>1398.761</v>
       </c>
       <c r="F54">
-        <v>4291.924000000001</v>
+        <v>4374.461</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5709,37 +5709,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M54">
-        <v>861.8183392000002</v>
+        <v>878.3917688</v>
       </c>
       <c r="N54">
-        <v>-467.5326249142859</v>
+        <v>-484.1060545142857</v>
       </c>
       <c r="O54">
-        <v>-120.6234172278858</v>
+        <v>-124.8993620646857</v>
       </c>
       <c r="P54">
-        <v>-346.9092076864001</v>
+        <v>-359.2066924496</v>
       </c>
       <c r="Q54">
-        <v>-6.909207686400123</v>
+        <v>-19.20669244959998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09373352837354319</v>
+        <v>0.09475339067936327</v>
       </c>
       <c r="T54">
-        <v>1.107009893153422</v>
+        <v>1.13056329513541</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1180361448099877</v>
+        <v>0.1158090477381011</v>
       </c>
       <c r="W54">
-        <v>0.1770983421221545</v>
+        <v>0.1775455432141893</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4575044372480143</v>
+        <v>0.4488722780546556</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1386332315228211</v>
+        <v>0.1401832315228211</v>
       </c>
       <c r="C55">
-        <v>-209.4557911585562</v>
+        <v>-335.1957192533337</v>
       </c>
       <c r="D55">
-        <v>4165.005208841444</v>
+        <v>4121.802280746667</v>
       </c>
       <c r="E55">
-        <v>1398.761</v>
+        <v>1481.298000000001</v>
       </c>
       <c r="F55">
-        <v>4374.461</v>
+        <v>4456.998000000001</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5791,37 +5791,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M55">
-        <v>878.3917688</v>
+        <v>894.9651984000001</v>
       </c>
       <c r="N55">
-        <v>-484.1060545142857</v>
+        <v>-500.6794841142857</v>
       </c>
       <c r="O55">
-        <v>-124.8993620646857</v>
+        <v>-129.1753069014857</v>
       </c>
       <c r="P55">
-        <v>-359.2066924496</v>
+        <v>-371.5041772128</v>
       </c>
       <c r="Q55">
-        <v>-19.20669244959998</v>
+        <v>-31.50417721280002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09475339067936327</v>
+        <v>0.09581759482456681</v>
       </c>
       <c r="T55">
-        <v>1.13056329513541</v>
+        <v>1.155140758073136</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1158090477381011</v>
+        <v>0.1136644357429511</v>
       </c>
       <c r="W55">
-        <v>0.1775455432141893</v>
+        <v>0.1779761813028154</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4488722780546556</v>
+        <v>0.4405598284610508</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1401832315228211</v>
+        <v>0.1417332315228211</v>
       </c>
       <c r="C56">
-        <v>-335.1957192533337</v>
+        <v>-460.0485747817243</v>
       </c>
       <c r="D56">
-        <v>4121.802280746667</v>
+        <v>4079.486425218277</v>
       </c>
       <c r="E56">
-        <v>1481.298000000001</v>
+        <v>1563.835000000001</v>
       </c>
       <c r="F56">
-        <v>4456.998000000001</v>
+        <v>4539.535000000001</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5873,37 +5873,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M56">
-        <v>894.9651984000001</v>
+        <v>911.5386280000001</v>
       </c>
       <c r="N56">
-        <v>-500.6794841142857</v>
+        <v>-517.2529137142858</v>
       </c>
       <c r="O56">
-        <v>-129.1753069014857</v>
+        <v>-133.4512517382857</v>
       </c>
       <c r="P56">
-        <v>-371.5041772128</v>
+        <v>-383.801661976</v>
       </c>
       <c r="Q56">
-        <v>-31.50417721280002</v>
+        <v>-43.80166197600005</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09581759482456681</v>
+        <v>0.09692909693177941</v>
       </c>
       <c r="T56">
-        <v>1.155140758073136</v>
+        <v>1.180810552696984</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1136644357429511</v>
+        <v>0.1115978096385338</v>
       </c>
       <c r="W56">
-        <v>0.1779761813028154</v>
+        <v>0.1783911598245824</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4405598284610508</v>
+        <v>0.4325496497617589</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1417332315228211</v>
+        <v>0.1432832315228211</v>
       </c>
       <c r="C57">
-        <v>-460.0485747817243</v>
+        <v>-584.0414010936038</v>
       </c>
       <c r="D57">
-        <v>4079.486425218277</v>
+        <v>4038.030598906397</v>
       </c>
       <c r="E57">
-        <v>1563.835000000001</v>
+        <v>1646.372000000001</v>
       </c>
       <c r="F57">
-        <v>4539.535000000001</v>
+        <v>4622.072000000001</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5955,37 +5955,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M57">
-        <v>911.5386280000001</v>
+        <v>928.1120576000002</v>
       </c>
       <c r="N57">
-        <v>-517.2529137142858</v>
+        <v>-533.8263433142859</v>
       </c>
       <c r="O57">
-        <v>-133.4512517382857</v>
+        <v>-137.7271965750857</v>
       </c>
       <c r="P57">
-        <v>-383.801661976</v>
+        <v>-396.0991467392001</v>
       </c>
       <c r="Q57">
-        <v>-43.80166197600005</v>
+        <v>-56.09914673920014</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09692909693177941</v>
+        <v>0.09809112186204713</v>
       </c>
       <c r="T57">
-        <v>1.180810552696984</v>
+        <v>1.20764715616737</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1115978096385338</v>
+        <v>0.1096049916092743</v>
       </c>
       <c r="W57">
-        <v>0.1783911598245824</v>
+        <v>0.1787913176848577</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4325496497617589</v>
+        <v>0.424825548873156</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1432832315228211</v>
+        <v>0.144833231522821</v>
       </c>
       <c r="C58">
-        <v>-584.0414010936038</v>
+        <v>-707.2001533368339</v>
       </c>
       <c r="D58">
-        <v>4038.030598906397</v>
+        <v>3997.408846663167</v>
       </c>
       <c r="E58">
-        <v>1646.372000000001</v>
+        <v>1728.909000000001</v>
       </c>
       <c r="F58">
-        <v>4622.072000000001</v>
+        <v>4704.609000000001</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6037,37 +6037,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M58">
-        <v>928.1120576000002</v>
+        <v>944.6854872000002</v>
       </c>
       <c r="N58">
-        <v>-533.8263433142859</v>
+        <v>-550.3997729142859</v>
       </c>
       <c r="O58">
-        <v>-137.7271965750857</v>
+        <v>-142.0031414118858</v>
       </c>
       <c r="P58">
-        <v>-396.0991467392001</v>
+        <v>-408.3966315024002</v>
       </c>
       <c r="Q58">
-        <v>-56.09914673920014</v>
+        <v>-68.39663150240017</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09809112186204713</v>
+        <v>0.09930719446349007</v>
       </c>
       <c r="T58">
-        <v>1.20764715616737</v>
+        <v>1.235731973752658</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1096049916092743</v>
+        <v>0.1076820970196379</v>
       </c>
       <c r="W58">
-        <v>0.1787913176848577</v>
+        <v>0.1791774349184567</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.424825548873156</v>
+        <v>0.4173724690683639</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.144833231522821</v>
+        <v>0.1463832315228211</v>
       </c>
       <c r="C59">
-        <v>-707.2001533368339</v>
+        <v>-829.5497526475542</v>
       </c>
       <c r="D59">
-        <v>3997.408846663167</v>
+        <v>3957.596247352446</v>
       </c>
       <c r="E59">
-        <v>1728.909000000001</v>
+        <v>1811.446000000001</v>
       </c>
       <c r="F59">
-        <v>4704.609000000001</v>
+        <v>4787.146000000001</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6119,37 +6119,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M59">
-        <v>944.6854872000002</v>
+        <v>961.2589168000002</v>
       </c>
       <c r="N59">
-        <v>-550.3997729142859</v>
+        <v>-566.9732025142858</v>
       </c>
       <c r="O59">
-        <v>-142.0031414118858</v>
+        <v>-146.2790862486858</v>
       </c>
       <c r="P59">
-        <v>-408.3966315024002</v>
+        <v>-420.6941162656001</v>
       </c>
       <c r="Q59">
-        <v>-68.39663150240017</v>
+        <v>-80.69411626560009</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09930719446349007</v>
+        <v>0.1005811752840494</v>
       </c>
       <c r="T59">
-        <v>1.235731973752658</v>
+        <v>1.265154163603911</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1076820970196379</v>
+        <v>0.105825509139989</v>
       </c>
       <c r="W59">
-        <v>0.1791774349184567</v>
+        <v>0.1795502377646902</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4173724690683639</v>
+        <v>0.4101763920154611</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.146383231522821</v>
+        <v>0.1479332315228211</v>
       </c>
       <c r="C60">
-        <v>-829.5497526475524</v>
+        <v>-951.1141371341246</v>
       </c>
       <c r="D60">
-        <v>3957.596247352447</v>
+        <v>3918.568862865875</v>
       </c>
       <c r="E60">
-        <v>1811.446</v>
+        <v>1893.983</v>
       </c>
       <c r="F60">
-        <v>4787.146</v>
+        <v>4869.683</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6201,37 +6201,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M60">
-        <v>961.2589168</v>
+        <v>977.8323464</v>
       </c>
       <c r="N60">
-        <v>-566.9732025142856</v>
+        <v>-583.5466321142857</v>
       </c>
       <c r="O60">
-        <v>-146.2790862486857</v>
+        <v>-150.5550310854857</v>
       </c>
       <c r="P60">
-        <v>-420.6941162655999</v>
+        <v>-432.9916010288</v>
       </c>
       <c r="Q60">
-        <v>-80.69411626559992</v>
+        <v>-92.99160102880001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1005811752840494</v>
+        <v>0.1019173015104896</v>
       </c>
       <c r="T60">
-        <v>1.265154163603911</v>
+        <v>1.296011582228397</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.105825509139989</v>
+        <v>0.104031856442701</v>
       </c>
       <c r="W60">
-        <v>0.1795502377646902</v>
+        <v>0.1799104032263057</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4101763920154612</v>
+        <v>0.4032242497779109</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1479332315228211</v>
+        <v>0.1494832315228211</v>
       </c>
       <c r="C61">
-        <v>-951.1141371341246</v>
+        <v>-1071.916309873896</v>
       </c>
       <c r="D61">
-        <v>3918.568862865875</v>
+        <v>3880.303690126104</v>
       </c>
       <c r="E61">
-        <v>1893.983</v>
+        <v>1976.52</v>
       </c>
       <c r="F61">
-        <v>4869.683</v>
+        <v>4952.22</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6283,37 +6283,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M61">
-        <v>977.8323464</v>
+        <v>994.4057760000001</v>
       </c>
       <c r="N61">
-        <v>-583.5466321142857</v>
+        <v>-600.1200617142857</v>
       </c>
       <c r="O61">
-        <v>-150.5550310854857</v>
+        <v>-154.8309759222857</v>
       </c>
       <c r="P61">
-        <v>-432.9916010288</v>
+        <v>-445.289085792</v>
       </c>
       <c r="Q61">
-        <v>-92.99160102880001</v>
+        <v>-105.289085792</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1019173015104896</v>
+        <v>0.1033202340482518</v>
       </c>
       <c r="T61">
-        <v>1.296011582228397</v>
+        <v>1.328411871784107</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.104031856442701</v>
+        <v>0.102297992168656</v>
       </c>
       <c r="W61">
-        <v>0.1799104032263057</v>
+        <v>0.1802585631725339</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4032242497779109</v>
+        <v>0.3965038456149458</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1494832315228211</v>
+        <v>0.1510332315228211</v>
       </c>
       <c r="C62">
-        <v>-1071.916309873896</v>
+        <v>-1191.978384125014</v>
       </c>
       <c r="D62">
-        <v>3880.303690126104</v>
+        <v>3842.778615874986</v>
       </c>
       <c r="E62">
-        <v>1976.52</v>
+        <v>2059.057000000001</v>
       </c>
       <c r="F62">
-        <v>4952.22</v>
+        <v>5034.757000000001</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6365,37 +6365,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M62">
-        <v>994.4057760000001</v>
+        <v>1010.9792056</v>
       </c>
       <c r="N62">
-        <v>-600.1200617142857</v>
+        <v>-616.6934913142858</v>
       </c>
       <c r="O62">
-        <v>-154.8309759222857</v>
+        <v>-159.1069207590857</v>
       </c>
       <c r="P62">
-        <v>-445.289085792</v>
+        <v>-457.5865705552001</v>
       </c>
       <c r="Q62">
-        <v>-105.289085792</v>
+        <v>-117.5865705552001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1033202340482518</v>
+        <v>0.1047951118443609</v>
       </c>
       <c r="T62">
-        <v>1.328411871784107</v>
+        <v>1.362473714650366</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.102297992168656</v>
+        <v>0.1006209759035961</v>
       </c>
       <c r="W62">
-        <v>0.1802585631725339</v>
+        <v>0.1805953080385579</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3965038456149458</v>
+        <v>0.3900037825720778</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1510332315228211</v>
+        <v>0.1525832315228211</v>
       </c>
       <c r="C63">
-        <v>-1191.978384125014</v>
+        <v>-1311.321625939984</v>
       </c>
       <c r="D63">
-        <v>3842.778615874986</v>
+        <v>3805.972374060017</v>
       </c>
       <c r="E63">
-        <v>2059.057000000001</v>
+        <v>2141.594000000001</v>
       </c>
       <c r="F63">
-        <v>5034.757000000001</v>
+        <v>5117.294000000001</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6447,37 +6447,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M63">
-        <v>1010.9792056</v>
+        <v>1027.5526352</v>
       </c>
       <c r="N63">
-        <v>-616.6934913142858</v>
+        <v>-633.2669209142858</v>
       </c>
       <c r="O63">
-        <v>-159.1069207590857</v>
+        <v>-163.3828655958858</v>
       </c>
       <c r="P63">
-        <v>-457.5865705552001</v>
+        <v>-469.8840553184001</v>
       </c>
       <c r="Q63">
-        <v>-117.5865705552001</v>
+        <v>-129.8840553184001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1047951118443609</v>
+        <v>0.1063476147876335</v>
       </c>
       <c r="T63">
-        <v>1.362473714650366</v>
+        <v>1.398328286088534</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1006209759035961</v>
+        <v>0.09899805693740903</v>
       </c>
       <c r="W63">
-        <v>0.1805953080385579</v>
+        <v>0.1809211901669683</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3900037825720778</v>
+        <v>0.3837133989822055</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1525832315228211</v>
+        <v>0.1541332315228211</v>
       </c>
       <c r="C64">
-        <v>-1311.321625939984</v>
+        <v>-1429.966494353554</v>
       </c>
       <c r="D64">
-        <v>3805.972374060017</v>
+        <v>3769.864505646446</v>
       </c>
       <c r="E64">
-        <v>2141.594000000001</v>
+        <v>2224.131</v>
       </c>
       <c r="F64">
-        <v>5117.294000000001</v>
+        <v>5199.831</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6529,37 +6529,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M64">
-        <v>1027.5526352</v>
+        <v>1044.1260648</v>
       </c>
       <c r="N64">
-        <v>-633.2669209142858</v>
+        <v>-649.8403505142857</v>
       </c>
       <c r="O64">
-        <v>-163.3828655958858</v>
+        <v>-167.6588104326857</v>
       </c>
       <c r="P64">
-        <v>-469.8840553184001</v>
+        <v>-482.1815400816</v>
       </c>
       <c r="Q64">
-        <v>-129.8840553184001</v>
+        <v>-142.1815400816</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1063476147876335</v>
+        <v>0.1079840368089209</v>
       </c>
       <c r="T64">
-        <v>1.398328286088534</v>
+        <v>1.436120942469305</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.09899805693740903</v>
+        <v>0.09742665920824381</v>
       </c>
       <c r="W64">
-        <v>0.1809211901669683</v>
+        <v>0.1812367268309847</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3837133989822055</v>
+        <v>0.3776227101094721</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1541332315228211</v>
+        <v>0.155683231522821</v>
       </c>
       <c r="C65">
-        <v>-1429.966494353554</v>
+        <v>-1547.932679304473</v>
       </c>
       <c r="D65">
-        <v>3769.864505646446</v>
+        <v>3734.435320695527</v>
       </c>
       <c r="E65">
-        <v>2224.131</v>
+        <v>2306.668000000001</v>
       </c>
       <c r="F65">
-        <v>5199.831</v>
+        <v>5282.368</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6611,37 +6611,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M65">
-        <v>1044.1260648</v>
+        <v>1060.6994944</v>
       </c>
       <c r="N65">
-        <v>-649.8403505142857</v>
+        <v>-666.4137801142857</v>
       </c>
       <c r="O65">
-        <v>-167.6588104326857</v>
+        <v>-171.9347552694857</v>
       </c>
       <c r="P65">
-        <v>-482.1815400816</v>
+        <v>-494.4790248448</v>
       </c>
       <c r="Q65">
-        <v>-142.1815400816</v>
+        <v>-154.4790248448</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1079840368089209</v>
+        <v>0.1097113711647243</v>
       </c>
       <c r="T65">
-        <v>1.436120942469305</v>
+        <v>1.47601319087123</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.09742665920824381</v>
+        <v>0.09590436765811501</v>
       </c>
       <c r="W65">
-        <v>0.1812367268309847</v>
+        <v>0.1815424029742505</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3776227101094721</v>
+        <v>0.3717223552640117</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.155683231522821</v>
+        <v>0.1572332315228211</v>
       </c>
       <c r="C66">
-        <v>-1547.932679304473</v>
+        <v>-1665.239137438833</v>
       </c>
       <c r="D66">
-        <v>3734.435320695527</v>
+        <v>3699.665862561168</v>
       </c>
       <c r="E66">
-        <v>2306.668000000001</v>
+        <v>2389.205000000001</v>
       </c>
       <c r="F66">
-        <v>5282.368</v>
+        <v>5364.905000000001</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6693,37 +6693,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M66">
-        <v>1060.6994944</v>
+        <v>1077.272924</v>
       </c>
       <c r="N66">
-        <v>-666.4137801142857</v>
+        <v>-682.9872097142858</v>
       </c>
       <c r="O66">
-        <v>-171.9347552694857</v>
+        <v>-176.2107001062857</v>
       </c>
       <c r="P66">
-        <v>-494.4790248448</v>
+        <v>-506.776509608</v>
       </c>
       <c r="Q66">
-        <v>-154.4790248448</v>
+        <v>-166.776509608</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1097113711647243</v>
+        <v>0.1115374103408592</v>
       </c>
       <c r="T66">
-        <v>1.47601319087123</v>
+        <v>1.518184996324694</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.09590436765811501</v>
+        <v>0.09442891584799015</v>
       </c>
       <c r="W66">
-        <v>0.1815424029742505</v>
+        <v>0.1818386736977236</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3717223552640117</v>
+        <v>0.3660035497984114</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1572332315228211</v>
+        <v>0.1587832315228211</v>
       </c>
       <c r="C67">
-        <v>-1665.239137438833</v>
+        <v>-1781.904125931774</v>
       </c>
       <c r="D67">
-        <v>3699.665862561168</v>
+        <v>3665.537874068227</v>
       </c>
       <c r="E67">
-        <v>2389.205000000001</v>
+        <v>2471.742000000001</v>
       </c>
       <c r="F67">
-        <v>5364.905000000001</v>
+        <v>5447.442000000001</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6775,37 +6775,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M67">
-        <v>1077.272924</v>
+        <v>1093.8463536</v>
       </c>
       <c r="N67">
-        <v>-682.9872097142858</v>
+        <v>-699.5606393142858</v>
       </c>
       <c r="O67">
-        <v>-176.2107001062857</v>
+        <v>-180.4866449430857</v>
       </c>
       <c r="P67">
-        <v>-506.776509608</v>
+        <v>-519.0739943712001</v>
       </c>
       <c r="Q67">
-        <v>-166.776509608</v>
+        <v>-179.0739943712001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1115374103408592</v>
+        <v>0.1134708635861786</v>
       </c>
       <c r="T67">
-        <v>1.518184996324694</v>
+        <v>1.562837496216597</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.09442891584799015</v>
+        <v>0.09299817469877818</v>
       </c>
       <c r="W67">
-        <v>0.1818386736977236</v>
+        <v>0.1821259665204853</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3660035497984114</v>
+        <v>0.3604580414681324</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1587832315228211</v>
+        <v>0.1603332315228211</v>
       </c>
       <c r="C68">
-        <v>-1781.904125931774</v>
+        <v>-1897.945234454349</v>
       </c>
       <c r="D68">
-        <v>3665.537874068227</v>
+        <v>3632.033765545652</v>
       </c>
       <c r="E68">
-        <v>2471.742000000001</v>
+        <v>2554.279000000001</v>
       </c>
       <c r="F68">
-        <v>5447.442000000001</v>
+        <v>5529.979000000001</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6857,37 +6857,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M68">
-        <v>1093.8463536</v>
+        <v>1110.4197832</v>
       </c>
       <c r="N68">
-        <v>-699.5606393142858</v>
+        <v>-716.1340689142859</v>
       </c>
       <c r="O68">
-        <v>-180.4866449430857</v>
+        <v>-184.7625897798858</v>
       </c>
       <c r="P68">
-        <v>-519.0739943712001</v>
+        <v>-531.3714791344001</v>
       </c>
       <c r="Q68">
-        <v>-179.0739943712001</v>
+        <v>-191.3714791344001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1134708635861786</v>
+        <v>0.1155214958160628</v>
       </c>
       <c r="T68">
-        <v>1.562837496216597</v>
+        <v>1.61019620822316</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.09299817469877818</v>
+        <v>0.09161014224058744</v>
       </c>
       <c r="W68">
-        <v>0.1821259665204853</v>
+        <v>0.18240468343809</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3604580414681324</v>
+        <v>0.3550780706999513</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1603332315228211</v>
+        <v>0.1618832315228211</v>
       </c>
       <c r="C69">
-        <v>-1897.945234454349</v>
+        <v>-2013.379415403147</v>
       </c>
       <c r="D69">
-        <v>3632.033765545652</v>
+        <v>3599.136584596853</v>
       </c>
       <c r="E69">
-        <v>2554.279000000001</v>
+        <v>2636.816000000001</v>
       </c>
       <c r="F69">
-        <v>5529.979000000001</v>
+        <v>5612.516000000001</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6939,37 +6939,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M69">
-        <v>1110.4197832</v>
+        <v>1126.9932128</v>
       </c>
       <c r="N69">
-        <v>-716.1340689142859</v>
+        <v>-732.7074985142857</v>
       </c>
       <c r="O69">
-        <v>-184.7625897798858</v>
+        <v>-189.0385346166857</v>
       </c>
       <c r="P69">
-        <v>-531.3714791344001</v>
+        <v>-543.6689638976</v>
       </c>
       <c r="Q69">
-        <v>-191.3714791344001</v>
+        <v>-203.6689638976</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1155214958160628</v>
+        <v>0.1177002925603148</v>
       </c>
       <c r="T69">
-        <v>1.61019620822316</v>
+        <v>1.660514839730134</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.09161014224058744</v>
+        <v>0.09026293426646119</v>
       </c>
       <c r="W69">
-        <v>0.18240468343809</v>
+        <v>0.1826752027992946</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3550780706999513</v>
+        <v>0.3498563343661286</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1618832315228211</v>
+        <v>0.1634332315228211</v>
       </c>
       <c r="C70">
-        <v>-2013.379415403147</v>
+        <v>-2128.22301250184</v>
       </c>
       <c r="D70">
-        <v>3599.136584596853</v>
+        <v>3566.829987498161</v>
       </c>
       <c r="E70">
-        <v>2636.816000000001</v>
+        <v>2719.353000000001</v>
       </c>
       <c r="F70">
-        <v>5612.516000000001</v>
+        <v>5695.053000000001</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7021,37 +7021,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M70">
-        <v>1126.9932128</v>
+        <v>1143.5666424</v>
       </c>
       <c r="N70">
-        <v>-732.7074985142857</v>
+        <v>-749.2809281142858</v>
       </c>
       <c r="O70">
-        <v>-189.0385346166857</v>
+        <v>-193.3144794534857</v>
       </c>
       <c r="P70">
-        <v>-543.6689638976</v>
+        <v>-555.9664486608001</v>
       </c>
       <c r="Q70">
-        <v>-203.6689638976</v>
+        <v>-215.9664486608001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1177002925603148</v>
+        <v>0.120019656836454</v>
       </c>
       <c r="T70">
-        <v>1.660514839730134</v>
+        <v>1.714079834560138</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.09026293426646119</v>
+        <v>0.08895477579883131</v>
       </c>
       <c r="W70">
-        <v>0.1826752027992946</v>
+        <v>0.1829378810195947</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3498563343661286</v>
+        <v>0.3447859527086484</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1634332315228211</v>
+        <v>0.1649832315228211</v>
       </c>
       <c r="C71">
-        <v>-2128.22301250184</v>
+        <v>-2242.491787876013</v>
       </c>
       <c r="D71">
-        <v>3566.829987498161</v>
+        <v>3535.098212123988</v>
       </c>
       <c r="E71">
-        <v>2719.353000000001</v>
+        <v>2801.890000000001</v>
       </c>
       <c r="F71">
-        <v>5695.053000000001</v>
+        <v>5777.590000000001</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7103,37 +7103,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M71">
-        <v>1143.5666424</v>
+        <v>1160.140072</v>
       </c>
       <c r="N71">
-        <v>-749.2809281142858</v>
+        <v>-765.8543577142858</v>
       </c>
       <c r="O71">
-        <v>-193.3144794534857</v>
+        <v>-197.5904242902857</v>
       </c>
       <c r="P71">
-        <v>-555.9664486608001</v>
+        <v>-568.263933424</v>
       </c>
       <c r="Q71">
-        <v>-215.9664486608001</v>
+        <v>-228.263933424</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.120019656836454</v>
+        <v>0.1224936453976691</v>
       </c>
       <c r="T71">
-        <v>1.714079834560138</v>
+        <v>1.771215829045476</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08895477579883131</v>
+        <v>0.08768399328741942</v>
       </c>
       <c r="W71">
-        <v>0.1829378810195947</v>
+        <v>0.1831930541478862</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3447859527086484</v>
+        <v>0.3398604390985249</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1649832315228211</v>
+        <v>0.1665332315228211</v>
       </c>
       <c r="C72">
-        <v>-2242.491787876013</v>
+        <v>-2356.200947695559</v>
       </c>
       <c r="D72">
-        <v>3535.098212123988</v>
+        <v>3503.926052304443</v>
       </c>
       <c r="E72">
-        <v>2801.890000000001</v>
+        <v>2884.427000000001</v>
       </c>
       <c r="F72">
-        <v>5777.590000000001</v>
+        <v>5860.127000000001</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7185,37 +7185,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M72">
-        <v>1160.140072</v>
+        <v>1176.7135016</v>
       </c>
       <c r="N72">
-        <v>-765.8543577142858</v>
+        <v>-782.4277873142859</v>
       </c>
       <c r="O72">
-        <v>-197.5904242902857</v>
+        <v>-201.8663691270858</v>
       </c>
       <c r="P72">
-        <v>-568.263933424</v>
+        <v>-580.5614181872002</v>
       </c>
       <c r="Q72">
-        <v>-228.263933424</v>
+        <v>-240.5614181872002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1224936453976691</v>
+        <v>0.1251382538596577</v>
       </c>
       <c r="T72">
-        <v>1.771215829045476</v>
+        <v>1.832292236943596</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08768399328741942</v>
+        <v>0.08644900746646984</v>
       </c>
       <c r="W72">
-        <v>0.1831930541478862</v>
+        <v>0.1834410393007329</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3398604390985249</v>
+        <v>0.3350736723506583</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1665332315228211</v>
+        <v>0.1680832315228211</v>
       </c>
       <c r="C73">
-        <v>-2356.200947695558</v>
+        <v>-2469.365166472236</v>
       </c>
       <c r="D73">
-        <v>3503.926052304443</v>
+        <v>3473.298833527765</v>
       </c>
       <c r="E73">
-        <v>2884.427000000001</v>
+        <v>2966.964000000001</v>
       </c>
       <c r="F73">
-        <v>5860.127</v>
+        <v>5942.664000000001</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7267,37 +7267,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M73">
-        <v>1176.7135016</v>
+        <v>1193.2869312</v>
       </c>
       <c r="N73">
-        <v>-782.4277873142859</v>
+        <v>-799.0012169142859</v>
       </c>
       <c r="O73">
-        <v>-201.8663691270858</v>
+        <v>-206.1423139638858</v>
       </c>
       <c r="P73">
-        <v>-580.5614181872002</v>
+        <v>-592.8589029504001</v>
       </c>
       <c r="Q73">
-        <v>-240.5614181872002</v>
+        <v>-252.8589029504001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1251382538596577</v>
+        <v>0.127971762926074</v>
       </c>
       <c r="T73">
-        <v>1.832292236943596</v>
+        <v>1.897731245405867</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08644900746646984</v>
+        <v>0.08524832680721332</v>
       </c>
       <c r="W73">
-        <v>0.1834410393007329</v>
+        <v>0.1836821359771116</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3350736723506583</v>
+        <v>0.3304198713457881</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1680832315228211</v>
+        <v>0.1696332315228211</v>
       </c>
       <c r="C74">
-        <v>-2469.365166472236</v>
+        <v>-2581.998610094006</v>
       </c>
       <c r="D74">
-        <v>3473.298833527765</v>
+        <v>3443.202389905994</v>
       </c>
       <c r="E74">
-        <v>2966.964000000001</v>
+        <v>3049.501</v>
       </c>
       <c r="F74">
-        <v>5942.664000000001</v>
+        <v>6025.201</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7349,37 +7349,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M74">
-        <v>1193.2869312</v>
+        <v>1209.8603608</v>
       </c>
       <c r="N74">
-        <v>-799.0012169142859</v>
+        <v>-815.5746465142857</v>
       </c>
       <c r="O74">
-        <v>-206.1423139638858</v>
+        <v>-210.4182588006857</v>
       </c>
       <c r="P74">
-        <v>-592.8589029504001</v>
+        <v>-605.1563877136</v>
       </c>
       <c r="Q74">
-        <v>-252.8589029504001</v>
+        <v>-265.1563877136</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.127971762926074</v>
+        <v>0.1310151615529657</v>
       </c>
       <c r="T74">
-        <v>1.897731245405867</v>
+        <v>1.968017587828306</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08524832680721332</v>
+        <v>0.08408054150848439</v>
       </c>
       <c r="W74">
-        <v>0.1836821359771116</v>
+        <v>0.1839166272650963</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3304198713457881</v>
+        <v>0.3258935717383116</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1696332315228211</v>
+        <v>0.1711832315228211</v>
       </c>
       <c r="C75">
-        <v>-2581.998610094006</v>
+        <v>-2694.11495767207</v>
       </c>
       <c r="D75">
-        <v>3443.202389905994</v>
+        <v>3413.62304232793</v>
       </c>
       <c r="E75">
-        <v>3049.501</v>
+        <v>3132.038</v>
       </c>
       <c r="F75">
-        <v>6025.201</v>
+        <v>6107.738</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7431,37 +7431,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M75">
-        <v>1209.8603608</v>
+        <v>1226.4337904</v>
       </c>
       <c r="N75">
-        <v>-815.5746465142857</v>
+        <v>-832.1480761142858</v>
       </c>
       <c r="O75">
-        <v>-210.4182588006857</v>
+        <v>-214.6942036374857</v>
       </c>
       <c r="P75">
-        <v>-605.1563877136</v>
+        <v>-617.4538724768</v>
       </c>
       <c r="Q75">
-        <v>-265.1563877136</v>
+        <v>-277.4538724768</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1310151615529657</v>
+        <v>0.1342926677665413</v>
       </c>
       <c r="T75">
-        <v>1.968017587828306</v>
+        <v>2.043710571975549</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08408054150848439</v>
+        <v>0.08294431797458594</v>
       </c>
       <c r="W75">
-        <v>0.1839166272650963</v>
+        <v>0.1841447809507032</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3258935717383116</v>
+        <v>0.3214896045526587</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1711832315228211</v>
+        <v>0.1727332315228211</v>
       </c>
       <c r="C76">
-        <v>-2694.11495767207</v>
+        <v>-2805.727422271425</v>
       </c>
       <c r="D76">
-        <v>3413.62304232793</v>
+        <v>3384.547577728575</v>
       </c>
       <c r="E76">
-        <v>3132.038</v>
+        <v>3214.575000000001</v>
       </c>
       <c r="F76">
-        <v>6107.738</v>
+        <v>6190.275000000001</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7513,37 +7513,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M76">
-        <v>1226.4337904</v>
+        <v>1243.00722</v>
       </c>
       <c r="N76">
-        <v>-832.1480761142858</v>
+        <v>-848.7215057142859</v>
       </c>
       <c r="O76">
-        <v>-214.6942036374857</v>
+        <v>-218.9701484742858</v>
       </c>
       <c r="P76">
-        <v>-617.4538724768</v>
+        <v>-629.7513572400001</v>
       </c>
       <c r="Q76">
-        <v>-277.4538724768</v>
+        <v>-289.7513572400001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1342926677665413</v>
+        <v>0.1378323744772029</v>
       </c>
       <c r="T76">
-        <v>2.043710571975549</v>
+        <v>2.125458994854571</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08294431797458594</v>
+        <v>0.0818383937349248</v>
       </c>
       <c r="W76">
-        <v>0.1841447809507032</v>
+        <v>0.1843668505380271</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3214896045526587</v>
+        <v>0.3172030764919566</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1727332315228211</v>
+        <v>0.174283231522821</v>
       </c>
       <c r="C77">
-        <v>-2805.727422271425</v>
+        <v>-2916.848770590939</v>
       </c>
       <c r="D77">
-        <v>3384.547577728575</v>
+        <v>3355.963229409062</v>
       </c>
       <c r="E77">
-        <v>3214.575000000001</v>
+        <v>3297.112000000001</v>
       </c>
       <c r="F77">
-        <v>6190.275000000001</v>
+        <v>6272.812000000001</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7595,37 +7595,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M77">
-        <v>1243.00722</v>
+        <v>1259.5806496</v>
       </c>
       <c r="N77">
-        <v>-848.7215057142859</v>
+        <v>-865.2949353142859</v>
       </c>
       <c r="O77">
-        <v>-218.9701484742858</v>
+        <v>-223.2460933110858</v>
       </c>
       <c r="P77">
-        <v>-629.7513572400001</v>
+        <v>-642.0488420032002</v>
       </c>
       <c r="Q77">
-        <v>-289.7513572400001</v>
+        <v>-302.0488420032002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1378323744772029</v>
+        <v>0.1416670567470864</v>
       </c>
       <c r="T77">
-        <v>2.125458994854571</v>
+        <v>2.214019786306845</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.0818383937349248</v>
+        <v>0.08076157276472841</v>
       </c>
       <c r="W77">
-        <v>0.1843668505380271</v>
+        <v>0.1845830761888425</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3172030764919566</v>
+        <v>0.3130293518012729</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.174283231522821</v>
+        <v>0.175833231522821</v>
       </c>
       <c r="C78">
-        <v>-2916.848770590939</v>
+        <v>-3027.491341654516</v>
       </c>
       <c r="D78">
-        <v>3355.963229409062</v>
+        <v>3327.857658345485</v>
       </c>
       <c r="E78">
-        <v>3297.112000000001</v>
+        <v>3379.649000000001</v>
       </c>
       <c r="F78">
-        <v>6272.812000000001</v>
+        <v>6355.349000000001</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7677,37 +7677,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M78">
-        <v>1259.5806496</v>
+        <v>1276.1540792</v>
       </c>
       <c r="N78">
-        <v>-865.2949353142859</v>
+        <v>-881.868364914286</v>
       </c>
       <c r="O78">
-        <v>-223.2460933110858</v>
+        <v>-227.5220381478858</v>
       </c>
       <c r="P78">
-        <v>-642.0488420032002</v>
+        <v>-654.3463267664001</v>
       </c>
       <c r="Q78">
-        <v>-302.0488420032002</v>
+        <v>-314.3463267664001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1416670567470864</v>
+        <v>0.1458351896491336</v>
       </c>
       <c r="T78">
-        <v>2.214019786306845</v>
+        <v>2.310281516146273</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.08076157276472841</v>
+        <v>0.07971272117038129</v>
       </c>
       <c r="W78">
-        <v>0.1845830761888425</v>
+        <v>0.1847936855889874</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3130293518012729</v>
+        <v>0.3089640355441136</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.175833231522821</v>
+        <v>0.1773832315228211</v>
       </c>
       <c r="C79">
-        <v>-3027.491341654516</v>
+        <v>-3137.667064570858</v>
       </c>
       <c r="D79">
-        <v>3327.857658345485</v>
+        <v>3300.218935429142</v>
       </c>
       <c r="E79">
-        <v>3379.649000000001</v>
+        <v>3462.186000000001</v>
       </c>
       <c r="F79">
-        <v>6355.349000000001</v>
+        <v>6437.886</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7759,37 +7759,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M79">
-        <v>1276.1540792</v>
+        <v>1292.7275088</v>
       </c>
       <c r="N79">
-        <v>-881.868364914286</v>
+        <v>-898.4417945142858</v>
       </c>
       <c r="O79">
-        <v>-227.5220381478858</v>
+        <v>-231.7979829846857</v>
       </c>
       <c r="P79">
-        <v>-654.3463267664001</v>
+        <v>-666.6438115296</v>
       </c>
       <c r="Q79">
-        <v>-314.3463267664001</v>
+        <v>-326.6438115296</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1458351896491336</v>
+        <v>0.1503822437240943</v>
       </c>
       <c r="T79">
-        <v>2.310281516146273</v>
+        <v>2.41529431233474</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07971272117038129</v>
+        <v>0.07869076320665845</v>
       </c>
       <c r="W79">
-        <v>0.1847936855889874</v>
+        <v>0.184998894748103</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3089640355441136</v>
+        <v>0.3050029581653428</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1773832315228211</v>
+        <v>0.1789332315228211</v>
       </c>
       <c r="C80">
-        <v>-3137.667064570858</v>
+        <v>-3247.387475415512</v>
       </c>
       <c r="D80">
-        <v>3300.218935429142</v>
+        <v>3273.035524584488</v>
       </c>
       <c r="E80">
-        <v>3462.186000000001</v>
+        <v>3544.723000000001</v>
       </c>
       <c r="F80">
-        <v>6437.886</v>
+        <v>6520.423000000001</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7841,37 +7841,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M80">
-        <v>1292.7275088</v>
+        <v>1309.3009384</v>
       </c>
       <c r="N80">
-        <v>-898.4417945142858</v>
+        <v>-915.0152241142858</v>
       </c>
       <c r="O80">
-        <v>-231.7979829846857</v>
+        <v>-236.0739278214858</v>
       </c>
       <c r="P80">
-        <v>-666.6438115296</v>
+        <v>-678.9412962928001</v>
       </c>
       <c r="Q80">
-        <v>-326.6438115296</v>
+        <v>-338.9412962928001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1503822437240943</v>
+        <v>0.1553623505680987</v>
       </c>
       <c r="T80">
-        <v>2.41529431233474</v>
+        <v>2.530308327207823</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07869076320665845</v>
+        <v>0.07769467759644759</v>
       </c>
       <c r="W80">
-        <v>0.184998894748103</v>
+        <v>0.1851989087386333</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3050029581653428</v>
+        <v>0.301142161226541</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1789332315228211</v>
+        <v>0.1804832315228211</v>
       </c>
       <c r="C81">
-        <v>-3247.387475415512</v>
+        <v>-3356.663733285413</v>
       </c>
       <c r="D81">
-        <v>3273.035524584488</v>
+        <v>3246.296266714588</v>
       </c>
       <c r="E81">
-        <v>3544.723000000001</v>
+        <v>3627.260000000001</v>
       </c>
       <c r="F81">
-        <v>6520.423000000001</v>
+        <v>6602.960000000001</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7923,37 +7923,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M81">
-        <v>1309.3009384</v>
+        <v>1325.874368</v>
       </c>
       <c r="N81">
-        <v>-915.0152241142858</v>
+        <v>-931.5886537142859</v>
       </c>
       <c r="O81">
-        <v>-236.0739278214858</v>
+        <v>-240.3498726582858</v>
       </c>
       <c r="P81">
-        <v>-678.9412962928001</v>
+        <v>-691.2387810560001</v>
       </c>
       <c r="Q81">
-        <v>-338.9412962928001</v>
+        <v>-351.2387810560001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1553623505680987</v>
+        <v>0.1608404680965037</v>
       </c>
       <c r="T81">
-        <v>2.530308327207823</v>
+        <v>2.656823743568214</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07769467759644759</v>
+        <v>0.07672349412649199</v>
       </c>
       <c r="W81">
-        <v>0.1851989087386333</v>
+        <v>0.1853939223794004</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.301142161226541</v>
+        <v>0.2973778842112093</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1804832315228211</v>
+        <v>0.1820332315228211</v>
       </c>
       <c r="C82">
-        <v>-3356.663733285413</v>
+        <v>-3465.506635572845</v>
       </c>
       <c r="D82">
-        <v>3246.296266714588</v>
+        <v>3219.990364427157</v>
       </c>
       <c r="E82">
-        <v>3627.260000000001</v>
+        <v>3709.797000000001</v>
       </c>
       <c r="F82">
-        <v>6602.960000000001</v>
+        <v>6685.497000000001</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8005,37 +8005,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M82">
-        <v>1325.874368</v>
+        <v>1342.4477976</v>
       </c>
       <c r="N82">
-        <v>-931.5886537142859</v>
+        <v>-948.162083314286</v>
       </c>
       <c r="O82">
-        <v>-240.3498726582858</v>
+        <v>-244.6258174950858</v>
       </c>
       <c r="P82">
-        <v>-691.2387810560001</v>
+        <v>-703.5362658192001</v>
       </c>
       <c r="Q82">
-        <v>-351.2387810560001</v>
+        <v>-363.5362658192001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1608404680965037</v>
+        <v>0.166895229575267</v>
       </c>
       <c r="T82">
-        <v>2.656823743568214</v>
+        <v>2.796656572177068</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.07672349412649199</v>
+        <v>0.07577629049530073</v>
       </c>
       <c r="W82">
-        <v>0.1853939223794004</v>
+        <v>0.1855841208685436</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2973778842112093</v>
+        <v>0.2937065523073672</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1820332315228211</v>
+        <v>0.1835832315228211</v>
       </c>
       <c r="C83">
-        <v>-3465.506635572845</v>
+        <v>-3573.926632502754</v>
       </c>
       <c r="D83">
-        <v>3219.990364427157</v>
+        <v>3194.107367497248</v>
       </c>
       <c r="E83">
-        <v>3709.797000000001</v>
+        <v>3792.334000000002</v>
       </c>
       <c r="F83">
-        <v>6685.497000000001</v>
+        <v>6768.034000000001</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8087,37 +8087,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M83">
-        <v>1342.4477976</v>
+        <v>1359.0212272</v>
       </c>
       <c r="N83">
-        <v>-948.162083314286</v>
+        <v>-964.735512914286</v>
       </c>
       <c r="O83">
-        <v>-244.6258174950858</v>
+        <v>-248.9017623318858</v>
       </c>
       <c r="P83">
-        <v>-703.5362658192001</v>
+        <v>-715.8337505824002</v>
       </c>
       <c r="Q83">
-        <v>-363.5362658192001</v>
+        <v>-375.8337505824002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.166895229575267</v>
+        <v>0.1736227423294485</v>
       </c>
       <c r="T83">
-        <v>2.796656572177068</v>
+        <v>2.952026381742461</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.07577629049530073</v>
+        <v>0.07485218939169949</v>
       </c>
       <c r="W83">
-        <v>0.1855841208685436</v>
+        <v>0.1857696803701468</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2937065523073672</v>
+        <v>0.2901247650841066</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1835832315228211</v>
+        <v>0.185133231522821</v>
       </c>
       <c r="C84">
-        <v>-3573.926632502754</v>
+        <v>-3681.933840974524</v>
       </c>
       <c r="D84">
-        <v>3194.107367497248</v>
+        <v>3168.637159025477</v>
       </c>
       <c r="E84">
-        <v>3792.334000000002</v>
+        <v>3874.871000000001</v>
       </c>
       <c r="F84">
-        <v>6768.034000000001</v>
+        <v>6850.571000000001</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8169,37 +8169,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M84">
-        <v>1359.0212272</v>
+        <v>1375.5946568</v>
       </c>
       <c r="N84">
-        <v>-964.735512914286</v>
+        <v>-981.3089425142858</v>
       </c>
       <c r="O84">
-        <v>-248.9017623318858</v>
+        <v>-253.1777071686857</v>
       </c>
       <c r="P84">
-        <v>-715.8337505824002</v>
+        <v>-728.1312353456001</v>
       </c>
       <c r="Q84">
-        <v>-375.8337505824002</v>
+        <v>-388.1312353456001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1736227423294485</v>
+        <v>0.1811417271723573</v>
       </c>
       <c r="T84">
-        <v>2.952026381742461</v>
+        <v>3.125674992433193</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.07485218939169949</v>
+        <v>0.0739503557845706</v>
       </c>
       <c r="W84">
-        <v>0.1857696803701468</v>
+        <v>0.1859507685584582</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2901247650841066</v>
+        <v>0.2866292859867078</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.185133231522821</v>
+        <v>0.1866832315228211</v>
       </c>
       <c r="C85">
-        <v>-3681.933840974524</v>
+        <v>-3789.538057746739</v>
       </c>
       <c r="D85">
-        <v>3168.637159025477</v>
+        <v>3143.569942253262</v>
       </c>
       <c r="E85">
-        <v>3874.871000000001</v>
+        <v>3957.408000000001</v>
       </c>
       <c r="F85">
-        <v>6850.571000000001</v>
+        <v>6933.108000000001</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8251,37 +8251,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M85">
-        <v>1375.5946568</v>
+        <v>1392.1680864</v>
       </c>
       <c r="N85">
-        <v>-981.3089425142858</v>
+        <v>-997.8823721142859</v>
       </c>
       <c r="O85">
-        <v>-253.1777071686857</v>
+        <v>-257.4536520054858</v>
       </c>
       <c r="P85">
-        <v>-728.1312353456001</v>
+        <v>-740.4287201088001</v>
       </c>
       <c r="Q85">
-        <v>-388.1312353456001</v>
+        <v>-400.4287201088001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1811417271723573</v>
+        <v>0.1896005851206297</v>
       </c>
       <c r="T85">
-        <v>3.125674992433193</v>
+        <v>3.321029679460269</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.0739503557845706</v>
+        <v>0.07306999440618285</v>
       </c>
       <c r="W85">
-        <v>0.1859507685584582</v>
+        <v>0.1861275451232385</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2866292859867078</v>
+        <v>0.2832170325821041</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.186683231522821</v>
+        <v>0.1882332315228211</v>
       </c>
       <c r="C86">
-        <v>-3789.538057746738</v>
+        <v>-3896.74877200102</v>
       </c>
       <c r="D86">
-        <v>3143.569942253262</v>
+        <v>3118.89622799898</v>
       </c>
       <c r="E86">
-        <v>3957.408</v>
+        <v>4039.945000000001</v>
       </c>
       <c r="F86">
-        <v>6933.108</v>
+        <v>7015.645</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8333,37 +8333,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M86">
-        <v>1392.1680864</v>
+        <v>1408.741516</v>
       </c>
       <c r="N86">
-        <v>-997.8823721142857</v>
+        <v>-1014.455801714286</v>
       </c>
       <c r="O86">
-        <v>-257.4536520054857</v>
+        <v>-261.7295968422857</v>
       </c>
       <c r="P86">
-        <v>-740.4287201088</v>
+        <v>-752.7262048719999</v>
       </c>
       <c r="Q86">
-        <v>-400.4287201088</v>
+        <v>-412.7262048719999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1896005851206296</v>
+        <v>0.1991872907953382</v>
       </c>
       <c r="T86">
-        <v>3.321029679460267</v>
+        <v>3.542431658090952</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.07306999440618286</v>
+        <v>0.07221034741316894</v>
       </c>
       <c r="W86">
-        <v>0.1861275451232385</v>
+        <v>0.1863001622394357</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2832170325821041</v>
+        <v>0.2798850674929029</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1882332315228211</v>
+        <v>0.1897832315228211</v>
       </c>
       <c r="C87">
-        <v>-3896.74877200102</v>
+        <v>-4003.575177318803</v>
       </c>
       <c r="D87">
-        <v>3118.89622799898</v>
+        <v>3094.606822681198</v>
       </c>
       <c r="E87">
-        <v>4039.945000000001</v>
+        <v>4122.482000000001</v>
       </c>
       <c r="F87">
-        <v>7015.645</v>
+        <v>7098.182000000001</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8415,37 +8415,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M87">
-        <v>1408.741516</v>
+        <v>1425.3149456</v>
       </c>
       <c r="N87">
-        <v>-1014.455801714286</v>
+        <v>-1031.029231314286</v>
       </c>
       <c r="O87">
-        <v>-261.7295968422857</v>
+        <v>-266.0055416790858</v>
       </c>
       <c r="P87">
-        <v>-752.7262048719999</v>
+        <v>-765.0236896352001</v>
       </c>
       <c r="Q87">
-        <v>-412.7262048719999</v>
+        <v>-425.0236896352001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1991872907953382</v>
+        <v>0.2101435258521481</v>
       </c>
       <c r="T87">
-        <v>3.542431658090952</v>
+        <v>3.795462490811734</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.07221034741316894</v>
+        <v>0.07137069221069024</v>
       </c>
       <c r="W87">
-        <v>0.1863001622394357</v>
+        <v>0.1864687650040934</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2798850674929029</v>
+        <v>0.2766305899639155</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1897832315228211</v>
+        <v>0.1913332315228211</v>
       </c>
       <c r="C88">
-        <v>-4003.575177318803</v>
+        <v>-4110.026183102788</v>
       </c>
       <c r="D88">
-        <v>3094.606822681198</v>
+        <v>3070.692816897213</v>
       </c>
       <c r="E88">
-        <v>4122.482000000001</v>
+        <v>4205.019000000001</v>
       </c>
       <c r="F88">
-        <v>7098.182000000001</v>
+        <v>7180.719000000001</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8497,37 +8497,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M88">
-        <v>1425.3149456</v>
+        <v>1441.8883752</v>
       </c>
       <c r="N88">
-        <v>-1031.029231314286</v>
+        <v>-1047.602660914286</v>
       </c>
       <c r="O88">
-        <v>-266.0055416790858</v>
+        <v>-270.2814865158858</v>
       </c>
       <c r="P88">
-        <v>-765.0236896352001</v>
+        <v>-777.3211743984002</v>
       </c>
       <c r="Q88">
-        <v>-425.0236896352001</v>
+        <v>-437.3211743984002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2101435258521481</v>
+        <v>0.2227853355330825</v>
       </c>
       <c r="T88">
-        <v>3.795462490811734</v>
+        <v>4.087421143951097</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.07137069221069024</v>
+        <v>0.07055033942665931</v>
       </c>
       <c r="W88">
-        <v>0.1864687650040934</v>
+        <v>0.1866334918431268</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2766305899639155</v>
+        <v>0.2734509280103073</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1913332315228211</v>
+        <v>0.1928832315228211</v>
       </c>
       <c r="C89">
-        <v>-4110.026183102788</v>
+        <v>-4216.110425472903</v>
       </c>
       <c r="D89">
-        <v>3070.692816897213</v>
+        <v>3047.145574527096</v>
       </c>
       <c r="E89">
-        <v>4205.019000000001</v>
+        <v>4287.556</v>
       </c>
       <c r="F89">
-        <v>7180.719000000001</v>
+        <v>7263.256</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8579,37 +8579,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M89">
-        <v>1441.8883752</v>
+        <v>1458.4618048</v>
       </c>
       <c r="N89">
-        <v>-1047.602660914286</v>
+        <v>-1064.176090514286</v>
       </c>
       <c r="O89">
-        <v>-270.2814865158858</v>
+        <v>-274.5574313526858</v>
       </c>
       <c r="P89">
-        <v>-777.3211743984002</v>
+        <v>-789.6186591616001</v>
       </c>
       <c r="Q89">
-        <v>-437.3211743984002</v>
+        <v>-449.6186591616001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2227853355330825</v>
+        <v>0.2375341134941728</v>
       </c>
       <c r="T89">
-        <v>4.087421143951097</v>
+        <v>4.42803957261369</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.07055033942665931</v>
+        <v>0.06974863102408363</v>
       </c>
       <c r="W89">
-        <v>0.1866334918431268</v>
+        <v>0.186794474890364</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2734509280103073</v>
+        <v>0.2703435311010992</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1928832315228211</v>
+        <v>0.1944332315228211</v>
       </c>
       <c r="C90">
-        <v>-4216.110425472903</v>
+        <v>-4321.836277664743</v>
       </c>
       <c r="D90">
-        <v>3047.145574527096</v>
+        <v>3023.956722335258</v>
       </c>
       <c r="E90">
-        <v>4287.556</v>
+        <v>4370.093000000001</v>
       </c>
       <c r="F90">
-        <v>7263.256</v>
+        <v>7345.793000000001</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8661,37 +8661,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M90">
-        <v>1458.4618048</v>
+        <v>1475.0352344</v>
       </c>
       <c r="N90">
-        <v>-1064.176090514286</v>
+        <v>-1080.749520114286</v>
       </c>
       <c r="O90">
-        <v>-274.5574313526858</v>
+        <v>-278.8333761894858</v>
       </c>
       <c r="P90">
-        <v>-789.6186591616001</v>
+        <v>-801.9161439248003</v>
       </c>
       <c r="Q90">
-        <v>-449.6186591616001</v>
+        <v>-461.9161439248003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2375341134941728</v>
+        <v>0.2549644874481885</v>
       </c>
       <c r="T90">
-        <v>4.42803957261369</v>
+        <v>4.83058862466948</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.06974863102408363</v>
+        <v>0.06896493854066696</v>
       </c>
       <c r="W90">
-        <v>0.186794474890364</v>
+        <v>0.1869518403410341</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2703435311010992</v>
+        <v>0.2673059633359184</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1944332315228211</v>
+        <v>0.1959832315228211</v>
       </c>
       <c r="C91">
-        <v>-4321.836277664743</v>
+        <v>-4427.211859956797</v>
       </c>
       <c r="D91">
-        <v>3023.956722335258</v>
+        <v>3001.118140043204</v>
       </c>
       <c r="E91">
-        <v>4370.093000000001</v>
+        <v>4452.630000000001</v>
       </c>
       <c r="F91">
-        <v>7345.793000000001</v>
+        <v>7428.330000000001</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8743,37 +8743,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M91">
-        <v>1475.0352344</v>
+        <v>1491.608664</v>
       </c>
       <c r="N91">
-        <v>-1080.749520114286</v>
+        <v>-1097.322949714286</v>
       </c>
       <c r="O91">
-        <v>-278.8333761894858</v>
+        <v>-283.1093210262858</v>
       </c>
       <c r="P91">
-        <v>-801.9161439248003</v>
+        <v>-814.2136286880002</v>
       </c>
       <c r="Q91">
-        <v>-461.9161439248003</v>
+        <v>-474.2136286880002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2549644874481885</v>
+        <v>0.2758809361930074</v>
       </c>
       <c r="T91">
-        <v>4.83058862466948</v>
+        <v>5.313647487136429</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.06896493854066696</v>
+        <v>0.06819866144577066</v>
       </c>
       <c r="W91">
-        <v>0.1869518403410341</v>
+        <v>0.1871057087816893</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2673059633359184</v>
+        <v>0.2643358970766304</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1959832315228211</v>
+        <v>0.1975332315228211</v>
       </c>
       <c r="C92">
-        <v>-4427.211859956797</v>
+        <v>-4532.245049151212</v>
       </c>
       <c r="D92">
-        <v>3001.118140043204</v>
+        <v>2978.621950848789</v>
       </c>
       <c r="E92">
-        <v>4452.630000000001</v>
+        <v>4535.167000000001</v>
       </c>
       <c r="F92">
-        <v>7428.330000000001</v>
+        <v>7510.867000000001</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8825,37 +8825,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M92">
-        <v>1491.608664</v>
+        <v>1508.1820936</v>
       </c>
       <c r="N92">
-        <v>-1097.322949714286</v>
+        <v>-1113.896379314286</v>
       </c>
       <c r="O92">
-        <v>-283.1093210262858</v>
+        <v>-287.3852658630859</v>
       </c>
       <c r="P92">
-        <v>-814.2136286880002</v>
+        <v>-826.5111134512003</v>
       </c>
       <c r="Q92">
-        <v>-474.2136286880002</v>
+        <v>-486.5111134512003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2758809361930074</v>
+        <v>0.3014454846588971</v>
       </c>
       <c r="T92">
-        <v>5.313647487136429</v>
+        <v>5.904052763484922</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.06819866144577066</v>
+        <v>0.06744922560570725</v>
       </c>
       <c r="W92">
-        <v>0.1871057087816893</v>
+        <v>0.187256195498374</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2643358970766304</v>
+        <v>0.2614311069988652</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1975332315228211</v>
+        <v>0.1990832315228211</v>
       </c>
       <c r="C93">
-        <v>-4532.245049151212</v>
+        <v>-4636.943487631309</v>
       </c>
       <c r="D93">
-        <v>2978.621950848789</v>
+        <v>2956.460512368692</v>
       </c>
       <c r="E93">
-        <v>4535.167000000001</v>
+        <v>4617.704000000002</v>
       </c>
       <c r="F93">
-        <v>7510.867000000001</v>
+        <v>7593.404000000001</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8907,37 +8907,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M93">
-        <v>1508.1820936</v>
+        <v>1524.7555232</v>
       </c>
       <c r="N93">
-        <v>-1113.896379314286</v>
+        <v>-1130.469808914286</v>
       </c>
       <c r="O93">
-        <v>-287.3852658630859</v>
+        <v>-291.6612106998858</v>
       </c>
       <c r="P93">
-        <v>-826.5111134512003</v>
+        <v>-838.8085982144004</v>
       </c>
       <c r="Q93">
-        <v>-486.5111134512003</v>
+        <v>-498.8085982144004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3014454846588971</v>
+        <v>0.3334011702412593</v>
       </c>
       <c r="T93">
-        <v>5.904052763484922</v>
+        <v>6.642059358920538</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.06744922560570725</v>
+        <v>0.06671608184912346</v>
       </c>
       <c r="W93">
-        <v>0.187256195498374</v>
+        <v>0.187403410764696</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2614311069988652</v>
+        <v>0.2585894645314862</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1990832315228211</v>
+        <v>0.2006332315228211</v>
       </c>
       <c r="C94">
-        <v>-4636.943487631309</v>
+        <v>-4741.314592017744</v>
       </c>
       <c r="D94">
-        <v>2956.460512368692</v>
+        <v>2934.626407982257</v>
       </c>
       <c r="E94">
-        <v>4617.704000000002</v>
+        <v>4700.241000000001</v>
       </c>
       <c r="F94">
-        <v>7593.404000000001</v>
+        <v>7675.941000000001</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8989,37 +8989,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M94">
-        <v>1524.7555232</v>
+        <v>1541.3289528</v>
       </c>
       <c r="N94">
-        <v>-1130.469808914286</v>
+        <v>-1147.043238514286</v>
       </c>
       <c r="O94">
-        <v>-291.6612106998858</v>
+        <v>-295.9371555366857</v>
       </c>
       <c r="P94">
-        <v>-838.8085982144004</v>
+        <v>-851.1060829776001</v>
       </c>
       <c r="Q94">
-        <v>-498.8085982144004</v>
+        <v>-511.1060829776001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3334011702412593</v>
+        <v>0.3744870517042964</v>
       </c>
       <c r="T94">
-        <v>6.642059358920538</v>
+        <v>7.590924981623473</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.06671608184912346</v>
+        <v>0.06599870462493936</v>
       </c>
       <c r="W94">
-        <v>0.187403410764696</v>
+        <v>0.1875474601113122</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2585894645314862</v>
+        <v>0.2558089326548038</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2006332315228211</v>
+        <v>0.2021832315228211</v>
       </c>
       <c r="C95">
-        <v>-4741.314592017744</v>
+        <v>-4845.365561443939</v>
       </c>
       <c r="D95">
-        <v>2934.626407982257</v>
+        <v>2913.112438556062</v>
       </c>
       <c r="E95">
-        <v>4700.241000000001</v>
+        <v>4782.778000000001</v>
       </c>
       <c r="F95">
-        <v>7675.941000000001</v>
+        <v>7758.478000000001</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9071,37 +9071,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M95">
-        <v>1541.3289528</v>
+        <v>1557.9023824</v>
       </c>
       <c r="N95">
-        <v>-1147.043238514286</v>
+        <v>-1163.616668114286</v>
       </c>
       <c r="O95">
-        <v>-295.9371555366857</v>
+        <v>-300.2131003734858</v>
       </c>
       <c r="P95">
-        <v>-851.1060829776001</v>
+        <v>-863.4035677408001</v>
       </c>
       <c r="Q95">
-        <v>-511.1060829776001</v>
+        <v>-523.4035677408001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3744870517042964</v>
+        <v>0.4292682269883458</v>
       </c>
       <c r="T95">
-        <v>7.590924981623473</v>
+        <v>8.856079145227387</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.06599870462493936</v>
+        <v>0.06529659074595062</v>
       </c>
       <c r="W95">
-        <v>0.1875474601113122</v>
+        <v>0.1876884445782131</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2558089326548038</v>
+        <v>0.2530875610308164</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2021832315228211</v>
+        <v>0.2037332315228211</v>
       </c>
       <c r="C96">
-        <v>-4845.365561443939</v>
+        <v>-4949.103385470136</v>
       </c>
       <c r="D96">
-        <v>2913.112438556062</v>
+        <v>2891.911614529865</v>
       </c>
       <c r="E96">
-        <v>4782.778000000001</v>
+        <v>4865.315000000001</v>
       </c>
       <c r="F96">
-        <v>7758.478000000001</v>
+        <v>7841.015000000001</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9153,37 +9153,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M96">
-        <v>1557.9023824</v>
+        <v>1574.475812</v>
       </c>
       <c r="N96">
-        <v>-1163.616668114286</v>
+        <v>-1180.190097714286</v>
       </c>
       <c r="O96">
-        <v>-300.2131003734858</v>
+        <v>-304.4890452102858</v>
       </c>
       <c r="P96">
-        <v>-863.4035677408001</v>
+        <v>-875.7010525040001</v>
       </c>
       <c r="Q96">
-        <v>-523.4035677408001</v>
+        <v>-535.7010525040001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4292682269883458</v>
+        <v>0.5059618723860153</v>
       </c>
       <c r="T96">
-        <v>8.856079145227387</v>
+        <v>10.62729497427287</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06529659074595062</v>
+        <v>0.06460925821178273</v>
       </c>
       <c r="W96">
-        <v>0.1876884445782131</v>
+        <v>0.187826460951074</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2530875610308164</v>
+        <v>0.2504234814410183</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2037332315228211</v>
+        <v>0.2052832315228211</v>
       </c>
       <c r="C97">
-        <v>-4949.103385470136</v>
+        <v>-5052.534851654365</v>
       </c>
       <c r="D97">
-        <v>2891.911614529865</v>
+        <v>2871.017148345637</v>
       </c>
       <c r="E97">
-        <v>4865.315000000001</v>
+        <v>4947.852000000002</v>
       </c>
       <c r="F97">
-        <v>7841.015000000001</v>
+        <v>7923.552000000001</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9235,37 +9235,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M97">
-        <v>1574.475812</v>
+        <v>1591.0492416</v>
       </c>
       <c r="N97">
-        <v>-1180.190097714286</v>
+        <v>-1196.763527314286</v>
       </c>
       <c r="O97">
-        <v>-304.4890452102858</v>
+        <v>-308.7649900470858</v>
       </c>
       <c r="P97">
-        <v>-875.7010525040001</v>
+        <v>-887.9985372672002</v>
       </c>
       <c r="Q97">
-        <v>-535.7010525040001</v>
+        <v>-547.9985372672002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5059618723860153</v>
+        <v>0.6210023404825193</v>
       </c>
       <c r="T97">
-        <v>10.62729497427287</v>
+        <v>13.28411871784109</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06460925821178273</v>
+        <v>0.06393624510540999</v>
       </c>
       <c r="W97">
-        <v>0.187826460951074</v>
+        <v>0.1879616019828337</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2504234814410183</v>
+        <v>0.2478149035093411</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.205283231522821</v>
+        <v>0.2068332315228211</v>
       </c>
       <c r="C98">
-        <v>-5052.534851654365</v>
+        <v>-5155.66655279758</v>
       </c>
       <c r="D98">
-        <v>2871.017148345636</v>
+        <v>2850.422447202421</v>
       </c>
       <c r="E98">
-        <v>4947.852000000001</v>
+        <v>5030.389000000001</v>
       </c>
       <c r="F98">
-        <v>7923.552000000001</v>
+        <v>8006.089000000001</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9317,37 +9317,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M98">
-        <v>1591.0492416</v>
+        <v>1607.6226712</v>
       </c>
       <c r="N98">
-        <v>-1196.763527314286</v>
+        <v>-1213.336956914286</v>
       </c>
       <c r="O98">
-        <v>-308.7649900470858</v>
+        <v>-313.0409348838858</v>
       </c>
       <c r="P98">
-        <v>-887.9985372672002</v>
+        <v>-900.2960220304002</v>
       </c>
       <c r="Q98">
-        <v>-547.9985372672002</v>
+        <v>-560.2960220304002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6210023404825178</v>
+        <v>0.8127364539766904</v>
       </c>
       <c r="T98">
-        <v>13.28411871784106</v>
+        <v>17.71215829045475</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.06393624510541</v>
+        <v>0.06327710855793155</v>
       </c>
       <c r="W98">
-        <v>0.1879616019828337</v>
+        <v>0.1880939566015674</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.247814903509341</v>
+        <v>0.245260110689657</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2068332315228211</v>
+        <v>0.2083832315228211</v>
       </c>
       <c r="C99">
-        <v>-5155.66655279758</v>
+        <v>-5258.504893879172</v>
       </c>
       <c r="D99">
-        <v>2850.422447202421</v>
+        <v>2830.121106120828</v>
       </c>
       <c r="E99">
-        <v>5030.389000000001</v>
+        <v>5112.926</v>
       </c>
       <c r="F99">
-        <v>8006.089000000001</v>
+        <v>8088.626</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9399,37 +9399,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M99">
-        <v>1607.6226712</v>
+        <v>1624.1961008</v>
       </c>
       <c r="N99">
-        <v>-1213.336956914286</v>
+        <v>-1229.910386514286</v>
       </c>
       <c r="O99">
-        <v>-313.0409348838858</v>
+        <v>-317.3168797206857</v>
       </c>
       <c r="P99">
-        <v>-900.2960220304002</v>
+        <v>-912.5935067936</v>
       </c>
       <c r="Q99">
-        <v>-560.2960220304002</v>
+        <v>-572.5935067936</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8127364539766904</v>
+        <v>1.196204680965036</v>
       </c>
       <c r="T99">
-        <v>17.71215829045475</v>
+        <v>26.56823743568212</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.06327710855793155</v>
+        <v>0.06263142377672816</v>
       </c>
       <c r="W99">
-        <v>0.1880939566015674</v>
+        <v>0.188223610105633</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.245260110689657</v>
+        <v>0.2427574564989464</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2083832315228211</v>
+        <v>0.2099332315228211</v>
       </c>
       <c r="C100">
-        <v>-5258.504893879172</v>
+        <v>-5361.056098698201</v>
       </c>
       <c r="D100">
-        <v>2830.121106120828</v>
+        <v>2810.1069013018</v>
       </c>
       <c r="E100">
-        <v>5112.926</v>
+        <v>5195.463000000001</v>
       </c>
       <c r="F100">
-        <v>8088.626</v>
+        <v>8171.163</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9481,37 +9481,37 @@
         <v>394.2857142857143</v>
       </c>
       <c r="M100">
-        <v>1624.1961008</v>
+        <v>1640.7695304</v>
       </c>
       <c r="N100">
-        <v>-1229.910386514286</v>
+        <v>-1246.483816114286</v>
       </c>
       <c r="O100">
-        <v>-317.3168797206857</v>
+        <v>-321.5928245574857</v>
       </c>
       <c r="P100">
-        <v>-912.5935067936</v>
+        <v>-924.8909915567999</v>
       </c>
       <c r="Q100">
-        <v>-572.5935067936</v>
+        <v>-584.8909915567999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.196204680965036</v>
+        <v>2.346609361930071</v>
       </c>
       <c r="T100">
-        <v>26.56823743568212</v>
+        <v>53.13647487136423</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.06263142377672816</v>
+        <v>0.06199878313251879</v>
       </c>
       <c r="W100">
-        <v>0.188223610105633</v>
+        <v>0.1883506443469902</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2427574564989464</v>
+        <v>0.2403053609787551</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2099332315228211</v>
-      </c>
-      <c r="C101">
-        <v>-5361.056098698201</v>
-      </c>
-      <c r="D101">
-        <v>2810.1069013018</v>
-      </c>
-      <c r="E101">
-        <v>5195.463000000001</v>
-      </c>
-      <c r="F101">
-        <v>8171.163</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>5278</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>734.2857142857143</v>
-      </c>
-      <c r="K101">
-        <v>340</v>
-      </c>
-      <c r="L101">
-        <v>394.2857142857143</v>
-      </c>
-      <c r="M101">
-        <v>1640.7695304</v>
-      </c>
-      <c r="N101">
-        <v>-1246.483816114286</v>
-      </c>
-      <c r="O101">
-        <v>-321.5928245574857</v>
-      </c>
-      <c r="P101">
-        <v>-924.8909915567999</v>
-      </c>
-      <c r="Q101">
-        <v>-584.8909915567999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.346609361930071</v>
-      </c>
-      <c r="T101">
-        <v>53.13647487136423</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.06199878313251879</v>
-      </c>
-      <c r="W101">
-        <v>0.1883506443469902</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2403053609787551</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
